--- a/research/traditional_assets/database/data/greece/greece_retail_rei_ts.xlsx
+++ b/research/traditional_assets/database/data/greece/greece_retail_rei_ts.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09176601402182294</v>
+        <v>0.09159922879097493</v>
       </c>
       <c r="C2">
-        <v>481.4720976803567</v>
+        <v>478.5322464551778</v>
       </c>
       <c r="D2">
-        <v>459.1720976803567</v>
+        <v>460.8442464551778</v>
       </c>
       <c r="E2">
-        <v>-255.6</v>
+        <v>-250.988</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.612</v>
       </c>
       <c r="G2">
         <v>22.3</v>
@@ -1445,28 +1445,28 @@
         <v>31.21</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2319836</v>
       </c>
       <c r="N2">
-        <v>31.21</v>
+        <v>30.9780164</v>
       </c>
       <c r="O2">
-        <v>6.866199999999999</v>
+        <v>6.815163608</v>
       </c>
       <c r="P2">
-        <v>24.3438</v>
+        <v>24.162852792</v>
       </c>
       <c r="Q2">
-        <v>24.7338</v>
+        <v>24.552852792</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09176601402182294</v>
+        <v>0.09212817049593426</v>
       </c>
       <c r="T2">
-        <v>0.5990912546403601</v>
+        <v>0.6038113675557083</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>134.5353723280439</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09159922879097493</v>
+        <v>0.09143244356012691</v>
       </c>
       <c r="C3">
-        <v>478.5322464551778</v>
+        <v>475.6046185385779</v>
       </c>
       <c r="D3">
-        <v>460.8442464551778</v>
+        <v>462.5286185385779</v>
       </c>
       <c r="E3">
-        <v>-250.988</v>
+        <v>-246.376</v>
       </c>
       <c r="F3">
-        <v>4.612</v>
+        <v>9.224</v>
       </c>
       <c r="G3">
         <v>22.3</v>
@@ -1527,28 +1527,28 @@
         <v>31.21</v>
       </c>
       <c r="M3">
-        <v>0.2319836</v>
+        <v>0.4639672</v>
       </c>
       <c r="N3">
-        <v>30.9780164</v>
+        <v>30.7460328</v>
       </c>
       <c r="O3">
-        <v>6.815163608</v>
+        <v>6.764127215999999</v>
       </c>
       <c r="P3">
-        <v>24.162852792</v>
+        <v>23.981905584</v>
       </c>
       <c r="Q3">
-        <v>24.552852792</v>
+        <v>24.371905584</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09212817049593426</v>
+        <v>0.09249771791849684</v>
       </c>
       <c r="T3">
-        <v>0.6038113675557083</v>
+        <v>0.6086278093060637</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>134.5353723280439</v>
+        <v>67.26768616402194</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09143244356012691</v>
+        <v>0.09126565832927891</v>
       </c>
       <c r="C4">
-        <v>475.6046185385779</v>
+        <v>472.6893484497136</v>
       </c>
       <c r="D4">
-        <v>462.5286185385779</v>
+        <v>464.2253484497136</v>
       </c>
       <c r="E4">
-        <v>-246.376</v>
+        <v>-241.764</v>
       </c>
       <c r="F4">
-        <v>9.224</v>
+        <v>13.836</v>
       </c>
       <c r="G4">
         <v>22.3</v>
@@ -1609,28 +1609,28 @@
         <v>31.21</v>
       </c>
       <c r="M4">
-        <v>0.4639672</v>
+        <v>0.6959507999999999</v>
       </c>
       <c r="N4">
-        <v>30.7460328</v>
+        <v>30.5140492</v>
       </c>
       <c r="O4">
-        <v>6.764127215999999</v>
+        <v>6.713090824</v>
       </c>
       <c r="P4">
-        <v>23.981905584</v>
+        <v>23.800958376</v>
       </c>
       <c r="Q4">
-        <v>24.371905584</v>
+        <v>24.190958376</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09249771791849684</v>
+        <v>0.09287488487554527</v>
       </c>
       <c r="T4">
-        <v>0.6086278093060637</v>
+        <v>0.613543559133746</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.26768616402194</v>
+        <v>44.84512410934796</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09126565832927891</v>
+        <v>0.0910988730984309</v>
       </c>
       <c r="C5">
-        <v>472.6893484497136</v>
+        <v>469.7865726888783</v>
       </c>
       <c r="D5">
-        <v>464.2253484497136</v>
+        <v>465.9345726888783</v>
       </c>
       <c r="E5">
-        <v>-241.764</v>
+        <v>-237.152</v>
       </c>
       <c r="F5">
-        <v>13.836</v>
+        <v>18.448</v>
       </c>
       <c r="G5">
         <v>22.3</v>
@@ -1691,28 +1691,28 @@
         <v>31.21</v>
       </c>
       <c r="M5">
-        <v>0.6959507999999999</v>
+        <v>0.9279343999999999</v>
       </c>
       <c r="N5">
-        <v>30.5140492</v>
+        <v>30.2820656</v>
       </c>
       <c r="O5">
-        <v>6.713090824</v>
+        <v>6.662054431999999</v>
       </c>
       <c r="P5">
-        <v>23.800958376</v>
+        <v>23.620011168</v>
       </c>
       <c r="Q5">
-        <v>24.190958376</v>
+        <v>24.010011168</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09287488487554527</v>
+        <v>0.09325990947753218</v>
       </c>
       <c r="T5">
-        <v>0.613543559133746</v>
+        <v>0.6185617204161717</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.84512410934796</v>
+        <v>33.63384308201097</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0910988730984309</v>
+        <v>0.09093208786758289</v>
       </c>
       <c r="C6">
-        <v>469.7865726888783</v>
+        <v>466.8964297741074</v>
       </c>
       <c r="D6">
-        <v>465.9345726888783</v>
+        <v>467.6564297741074</v>
       </c>
       <c r="E6">
-        <v>-237.152</v>
+        <v>-232.54</v>
       </c>
       <c r="F6">
-        <v>18.448</v>
+        <v>23.06</v>
       </c>
       <c r="G6">
         <v>22.3</v>
@@ -1773,28 +1773,28 @@
         <v>31.21</v>
       </c>
       <c r="M6">
-        <v>0.9279343999999999</v>
+        <v>1.159918</v>
       </c>
       <c r="N6">
-        <v>30.2820656</v>
+        <v>30.050082</v>
       </c>
       <c r="O6">
-        <v>6.662054431999999</v>
+        <v>6.611018039999999</v>
       </c>
       <c r="P6">
-        <v>23.620011168</v>
+        <v>23.43906396</v>
       </c>
       <c r="Q6">
-        <v>24.010011168</v>
+        <v>23.82906396</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09325990947753218</v>
+        <v>0.09365303986061357</v>
       </c>
       <c r="T6">
-        <v>0.6185617204161717</v>
+        <v>0.6236855271992802</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.63384308201097</v>
+        <v>26.90707446560877</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09093208786758289</v>
+        <v>0.09076530263673487</v>
       </c>
       <c r="C7">
-        <v>466.8964297741074</v>
+        <v>464.0190602786004</v>
       </c>
       <c r="D7">
-        <v>467.6564297741074</v>
+        <v>469.3910602786004</v>
       </c>
       <c r="E7">
-        <v>-232.54</v>
+        <v>-227.928</v>
       </c>
       <c r="F7">
-        <v>23.06</v>
+        <v>27.672</v>
       </c>
       <c r="G7">
         <v>22.3</v>
@@ -1855,28 +1855,28 @@
         <v>31.21</v>
       </c>
       <c r="M7">
-        <v>1.159918</v>
+        <v>1.3919016</v>
       </c>
       <c r="N7">
-        <v>30.050082</v>
+        <v>29.8180984</v>
       </c>
       <c r="O7">
-        <v>6.611018039999999</v>
+        <v>6.559981647999999</v>
       </c>
       <c r="P7">
-        <v>23.43906396</v>
+        <v>23.258116752</v>
       </c>
       <c r="Q7">
-        <v>23.82906396</v>
+        <v>23.648116752</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09365303986061357</v>
+        <v>0.09405453471993071</v>
       </c>
       <c r="T7">
-        <v>0.6236855271992802</v>
+        <v>0.6289183511479864</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.90707446560877</v>
+        <v>22.42256205467398</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09076530263673487</v>
+        <v>0.09059851740588687</v>
       </c>
       <c r="C8">
-        <v>464.0190602786005</v>
+        <v>461.1546068689764</v>
       </c>
       <c r="D8">
-        <v>469.3910602786004</v>
+        <v>471.1386068689764</v>
       </c>
       <c r="E8">
-        <v>-227.928</v>
+        <v>-223.316</v>
       </c>
       <c r="F8">
-        <v>27.672</v>
+        <v>32.284</v>
       </c>
       <c r="G8">
         <v>22.3</v>
@@ -1937,28 +1937,28 @@
         <v>31.21</v>
       </c>
       <c r="M8">
-        <v>1.3919016</v>
+        <v>1.6238852</v>
       </c>
       <c r="N8">
-        <v>29.8180984</v>
+        <v>29.5861148</v>
       </c>
       <c r="O8">
-        <v>6.559981647999999</v>
+        <v>6.508945256</v>
       </c>
       <c r="P8">
-        <v>23.258116752</v>
+        <v>23.077169544</v>
       </c>
       <c r="Q8">
-        <v>23.648116752</v>
+        <v>23.467169544</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09405453471993071</v>
+        <v>0.0944646638772977</v>
       </c>
       <c r="T8">
-        <v>0.6289183511479864</v>
+        <v>0.6342637089450521</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.42256205467398</v>
+        <v>19.21933890400627</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09059851740588687</v>
+        <v>0.09043173217503886</v>
       </c>
       <c r="C9">
-        <v>461.1546068689764</v>
+        <v>458.3032143443904</v>
       </c>
       <c r="D9">
-        <v>471.1386068689764</v>
+        <v>472.8992143443904</v>
       </c>
       <c r="E9">
-        <v>-223.316</v>
+        <v>-218.704</v>
       </c>
       <c r="F9">
-        <v>32.284</v>
+        <v>36.896</v>
       </c>
       <c r="G9">
         <v>22.3</v>
@@ -2019,28 +2019,28 @@
         <v>31.21</v>
       </c>
       <c r="M9">
-        <v>1.6238852</v>
+        <v>1.8558688</v>
       </c>
       <c r="N9">
-        <v>29.5861148</v>
+        <v>29.3541312</v>
       </c>
       <c r="O9">
-        <v>6.508945256</v>
+        <v>6.457908863999999</v>
       </c>
       <c r="P9">
-        <v>23.077169544</v>
+        <v>22.896222336</v>
       </c>
       <c r="Q9">
-        <v>23.467169544</v>
+        <v>23.286222336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09446466387729771</v>
+        <v>0.0948837088859118</v>
       </c>
       <c r="T9">
-        <v>0.6342637089450522</v>
+        <v>0.6397252701724888</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.21933890400627</v>
+        <v>16.81692154100548</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09043173217503886</v>
+        <v>0.09026494694419085</v>
       </c>
       <c r="C10">
-        <v>458.3032143443904</v>
+        <v>455.4650296765276</v>
       </c>
       <c r="D10">
-        <v>472.8992143443904</v>
+        <v>474.6730296765276</v>
       </c>
       <c r="E10">
-        <v>-218.704</v>
+        <v>-214.092</v>
       </c>
       <c r="F10">
-        <v>36.896</v>
+        <v>41.508</v>
       </c>
       <c r="G10">
         <v>22.3</v>
@@ -2101,28 +2101,28 @@
         <v>31.21</v>
       </c>
       <c r="M10">
-        <v>1.8558688</v>
+        <v>2.0878524</v>
       </c>
       <c r="N10">
-        <v>29.3541312</v>
+        <v>29.1221476</v>
       </c>
       <c r="O10">
-        <v>6.457908863999999</v>
+        <v>6.406872472</v>
       </c>
       <c r="P10">
-        <v>22.896222336</v>
+        <v>22.715275128</v>
       </c>
       <c r="Q10">
-        <v>23.286222336</v>
+        <v>23.105275128</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0948837088859118</v>
+        <v>0.095311963674935</v>
       </c>
       <c r="T10">
-        <v>0.6397252701724888</v>
+        <v>0.6453068657126164</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.81692154100548</v>
+        <v>14.94837470311599</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09026494694419085</v>
+        <v>0.09009816171334281</v>
       </c>
       <c r="C11">
-        <v>455.4650296765276</v>
+        <v>452.640202050502</v>
       </c>
       <c r="D11">
-        <v>474.6730296765276</v>
+        <v>476.460202050502</v>
       </c>
       <c r="E11">
-        <v>-214.092</v>
+        <v>-209.48</v>
       </c>
       <c r="F11">
-        <v>41.508</v>
+        <v>46.12</v>
       </c>
       <c r="G11">
         <v>22.3</v>
@@ -2183,28 +2183,28 @@
         <v>31.21</v>
       </c>
       <c r="M11">
-        <v>2.0878524</v>
+        <v>2.319836</v>
       </c>
       <c r="N11">
-        <v>29.1221476</v>
+        <v>28.890164</v>
       </c>
       <c r="O11">
-        <v>6.406872472</v>
+        <v>6.35583608</v>
       </c>
       <c r="P11">
-        <v>22.715275128</v>
+        <v>22.53432792</v>
       </c>
       <c r="Q11">
-        <v>23.105275128</v>
+        <v>22.92432792</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.095311963674935</v>
+        <v>0.09574973523704758</v>
       </c>
       <c r="T11">
-        <v>0.6453068657126164</v>
+        <v>0.6510124967091913</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.94837470311599</v>
+        <v>13.45353723280439</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09009816171334281</v>
+        <v>0.09006007648249482</v>
       </c>
       <c r="C12">
-        <v>452.640202050502</v>
+        <v>448.4381899725099</v>
       </c>
       <c r="D12">
-        <v>476.460202050502</v>
+        <v>476.8701899725099</v>
       </c>
       <c r="E12">
-        <v>-209.48</v>
+        <v>-204.868</v>
       </c>
       <c r="F12">
-        <v>46.12</v>
+        <v>50.732</v>
       </c>
       <c r="G12">
         <v>22.3</v>
@@ -2265,45 +2265,45 @@
         <v>31.21</v>
       </c>
       <c r="M12">
-        <v>2.319836</v>
+        <v>2.6279176</v>
       </c>
       <c r="N12">
-        <v>28.890164</v>
+        <v>28.5820824</v>
       </c>
       <c r="O12">
-        <v>6.35583608</v>
+        <v>6.288058127999999</v>
       </c>
       <c r="P12">
-        <v>22.53432792</v>
+        <v>22.294024272</v>
       </c>
       <c r="Q12">
-        <v>22.92432792</v>
+        <v>22.684024272</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09574973523704758</v>
+        <v>0.09619734436235373</v>
       </c>
       <c r="T12">
-        <v>0.6510124967091913</v>
+        <v>0.6568463441326555</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.45353723280439</v>
+        <v>11.87632367164024</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09006007648249482</v>
+        <v>0.08990499125164682</v>
       </c>
       <c r="C13">
-        <v>448.4381899725099</v>
+        <v>445.5029961887147</v>
       </c>
       <c r="D13">
-        <v>476.8701899725099</v>
+        <v>478.5469961887147</v>
       </c>
       <c r="E13">
-        <v>-204.868</v>
+        <v>-200.256</v>
       </c>
       <c r="F13">
-        <v>50.732</v>
+        <v>55.34399999999999</v>
       </c>
       <c r="G13">
         <v>22.3</v>
@@ -2347,28 +2347,28 @@
         <v>31.21</v>
       </c>
       <c r="M13">
-        <v>2.6279176</v>
+        <v>2.8668192</v>
       </c>
       <c r="N13">
-        <v>28.5820824</v>
+        <v>28.3431808</v>
       </c>
       <c r="O13">
-        <v>6.288058127999999</v>
+        <v>6.235499776</v>
       </c>
       <c r="P13">
-        <v>22.294024272</v>
+        <v>22.107681024</v>
       </c>
       <c r="Q13">
-        <v>22.684024272</v>
+        <v>22.497681024</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09619734436235373</v>
+        <v>0.09665512642232593</v>
       </c>
       <c r="T13">
-        <v>0.6568463441326555</v>
+        <v>0.6628127789975621</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.87632367164024</v>
+        <v>10.88663003233689</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08990499125164682</v>
+        <v>0.08974990602079878</v>
       </c>
       <c r="C14">
-        <v>445.5029961887147</v>
+        <v>442.5796362358728</v>
       </c>
       <c r="D14">
-        <v>478.5469961887147</v>
+        <v>480.2356362358728</v>
       </c>
       <c r="E14">
-        <v>-200.256</v>
+        <v>-195.644</v>
       </c>
       <c r="F14">
-        <v>55.34399999999999</v>
+        <v>59.956</v>
       </c>
       <c r="G14">
         <v>22.3</v>
@@ -2429,28 +2429,28 @@
         <v>31.21</v>
       </c>
       <c r="M14">
-        <v>2.8668192</v>
+        <v>3.1057208</v>
       </c>
       <c r="N14">
-        <v>28.3431808</v>
+        <v>28.1042792</v>
       </c>
       <c r="O14">
-        <v>6.235499776</v>
+        <v>6.182941423999999</v>
       </c>
       <c r="P14">
-        <v>22.107681024</v>
+        <v>21.921337776</v>
       </c>
       <c r="Q14">
-        <v>22.497681024</v>
+        <v>22.311337776</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09665512642232593</v>
+        <v>0.09712343220781471</v>
       </c>
       <c r="T14">
-        <v>0.6628127789975621</v>
+        <v>0.6689163732846503</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.88663003233689</v>
+        <v>10.04919695292635</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08974990602079878</v>
+        <v>0.08978046078995079</v>
       </c>
       <c r="C15">
-        <v>442.5796362358728</v>
+        <v>437.6339996904571</v>
       </c>
       <c r="D15">
-        <v>480.2356362358728</v>
+        <v>479.9019996904571</v>
       </c>
       <c r="E15">
-        <v>-195.644</v>
+        <v>-191.032</v>
       </c>
       <c r="F15">
-        <v>59.956</v>
+        <v>64.568</v>
       </c>
       <c r="G15">
         <v>22.3</v>
@@ -2511,45 +2511,45 @@
         <v>31.21</v>
       </c>
       <c r="M15">
-        <v>3.1057208</v>
+        <v>3.454388</v>
       </c>
       <c r="N15">
-        <v>28.1042792</v>
+        <v>27.755612</v>
       </c>
       <c r="O15">
-        <v>6.182941423999999</v>
+        <v>6.10623464</v>
       </c>
       <c r="P15">
-        <v>21.921337776</v>
+        <v>21.64937736</v>
       </c>
       <c r="Q15">
-        <v>22.311337776</v>
+        <v>22.03937736</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09712343220781471</v>
+        <v>0.09760262882552417</v>
       </c>
       <c r="T15">
-        <v>0.6689163732846503</v>
+        <v>0.6751619116249268</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.04919695292635</v>
+        <v>9.034885484780517</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08978046078995079</v>
+        <v>0.08963863555910277</v>
       </c>
       <c r="C16">
-        <v>437.6339996904571</v>
+        <v>434.5745619685135</v>
       </c>
       <c r="D16">
-        <v>479.9019996904571</v>
+        <v>481.4545619685135</v>
       </c>
       <c r="E16">
-        <v>-191.032</v>
+        <v>-186.42</v>
       </c>
       <c r="F16">
-        <v>64.568</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="G16">
         <v>22.3</v>
@@ -2593,28 +2593,28 @@
         <v>31.21</v>
       </c>
       <c r="M16">
-        <v>3.454388</v>
+        <v>3.70113</v>
       </c>
       <c r="N16">
-        <v>27.755612</v>
+        <v>27.50887</v>
       </c>
       <c r="O16">
-        <v>6.10623464</v>
+        <v>6.051951399999999</v>
       </c>
       <c r="P16">
-        <v>21.64937736</v>
+        <v>21.4569186</v>
       </c>
       <c r="Q16">
-        <v>22.03937736</v>
+        <v>21.8469186</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09760262882552417</v>
+        <v>0.09809310065776797</v>
       </c>
       <c r="T16">
-        <v>0.6751619116249268</v>
+        <v>0.6815544038085037</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.034885484780517</v>
+        <v>8.432559785795148</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08963863555910277</v>
+        <v>0.08949681032825477</v>
       </c>
       <c r="C17">
-        <v>434.5745619685135</v>
+        <v>431.5252024422932</v>
       </c>
       <c r="D17">
-        <v>481.4545619685135</v>
+        <v>483.0172024422932</v>
       </c>
       <c r="E17">
-        <v>-186.42</v>
+        <v>-181.808</v>
       </c>
       <c r="F17">
-        <v>69.17999999999999</v>
+        <v>73.792</v>
       </c>
       <c r="G17">
         <v>22.3</v>
@@ -2675,28 +2675,28 @@
         <v>31.21</v>
       </c>
       <c r="M17">
-        <v>3.70113</v>
+        <v>3.947872</v>
       </c>
       <c r="N17">
-        <v>27.50887</v>
+        <v>27.262128</v>
       </c>
       <c r="O17">
-        <v>6.051951399999999</v>
+        <v>5.997668159999999</v>
       </c>
       <c r="P17">
-        <v>21.4569186</v>
+        <v>21.26445984</v>
       </c>
       <c r="Q17">
-        <v>21.8469186</v>
+        <v>21.65445984</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09809310065776797</v>
+        <v>0.09859525039077949</v>
       </c>
       <c r="T17">
-        <v>0.6815544038085037</v>
+        <v>0.6880990981869278</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.432559785795149</v>
+        <v>7.905524799182952</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08949681032825477</v>
+        <v>0.08946106509740674</v>
       </c>
       <c r="C18">
-        <v>431.5252024422932</v>
+        <v>427.308647706085</v>
       </c>
       <c r="D18">
-        <v>483.0172024422932</v>
+        <v>483.412647706085</v>
       </c>
       <c r="E18">
-        <v>-181.808</v>
+        <v>-177.196</v>
       </c>
       <c r="F18">
-        <v>73.792</v>
+        <v>78.40400000000001</v>
       </c>
       <c r="G18">
         <v>22.3</v>
@@ -2757,45 +2757,45 @@
         <v>31.21</v>
       </c>
       <c r="M18">
-        <v>3.947872</v>
+        <v>4.2573372</v>
       </c>
       <c r="N18">
-        <v>27.262128</v>
+        <v>26.9526628</v>
       </c>
       <c r="O18">
-        <v>5.997668159999999</v>
+        <v>5.929585815999999</v>
       </c>
       <c r="P18">
-        <v>21.26445984</v>
+        <v>21.023076984</v>
       </c>
       <c r="Q18">
-        <v>21.65445984</v>
+        <v>21.413076984</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09859525039077949</v>
+        <v>0.09910950011735753</v>
       </c>
       <c r="T18">
-        <v>0.6880990981869278</v>
+        <v>0.6948014960443502</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.905524799182952</v>
+        <v>7.330873391940859</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08946106509740674</v>
+        <v>0.08932547986655874</v>
       </c>
       <c r="C19">
-        <v>427.308647706085</v>
+        <v>424.2025154331041</v>
       </c>
       <c r="D19">
-        <v>483.412647706085</v>
+        <v>484.9185154331041</v>
       </c>
       <c r="E19">
-        <v>-177.196</v>
+        <v>-172.584</v>
       </c>
       <c r="F19">
-        <v>78.40400000000001</v>
+        <v>83.01600000000001</v>
       </c>
       <c r="G19">
         <v>22.3</v>
@@ -2839,28 +2839,28 @@
         <v>31.21</v>
       </c>
       <c r="M19">
-        <v>4.2573372</v>
+        <v>4.5077688</v>
       </c>
       <c r="N19">
-        <v>26.9526628</v>
+        <v>26.7022312</v>
       </c>
       <c r="O19">
-        <v>5.929585815999999</v>
+        <v>5.874490863999999</v>
       </c>
       <c r="P19">
-        <v>21.023076984</v>
+        <v>20.827740336</v>
       </c>
       <c r="Q19">
-        <v>21.413076984</v>
+        <v>21.217740336</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09910950011735753</v>
+        <v>0.0996362925201936</v>
       </c>
       <c r="T19">
-        <v>0.6948014960443502</v>
+        <v>0.7016673670202462</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.330873391940859</v>
+        <v>6.923602647944144</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08932547986655874</v>
+        <v>0.08918989463571074</v>
       </c>
       <c r="C20">
-        <v>424.2025154331041</v>
+        <v>421.1057942649489</v>
       </c>
       <c r="D20">
-        <v>484.9185154331041</v>
+        <v>486.4337942649489</v>
       </c>
       <c r="E20">
-        <v>-172.584</v>
+        <v>-167.972</v>
       </c>
       <c r="F20">
-        <v>83.01599999999999</v>
+        <v>87.628</v>
       </c>
       <c r="G20">
         <v>22.3</v>
@@ -2921,28 +2921,28 @@
         <v>31.21</v>
       </c>
       <c r="M20">
-        <v>4.5077688</v>
+        <v>4.7582004</v>
       </c>
       <c r="N20">
-        <v>26.7022312</v>
+        <v>26.4517996</v>
       </c>
       <c r="O20">
-        <v>5.874490863999999</v>
+        <v>5.819395911999999</v>
       </c>
       <c r="P20">
-        <v>20.827740336</v>
+        <v>20.632403688</v>
       </c>
       <c r="Q20">
-        <v>21.217740336</v>
+        <v>21.022403688</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09963629252019358</v>
+        <v>0.1001760921428528</v>
       </c>
       <c r="T20">
-        <v>0.701667367020246</v>
+        <v>0.7087027656745593</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.923602647944144</v>
+        <v>6.559202508578664</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08918989463571074</v>
+        <v>0.08905430940486272</v>
       </c>
       <c r="C21">
-        <v>421.1057942649489</v>
+        <v>418.0185727019448</v>
       </c>
       <c r="D21">
-        <v>486.4337942649489</v>
+        <v>487.9585727019448</v>
       </c>
       <c r="E21">
-        <v>-167.972</v>
+        <v>-163.36</v>
       </c>
       <c r="F21">
-        <v>87.628</v>
+        <v>92.24000000000001</v>
       </c>
       <c r="G21">
         <v>22.3</v>
@@ -3003,28 +3003,28 @@
         <v>31.21</v>
       </c>
       <c r="M21">
-        <v>4.7582004</v>
+        <v>5.008632</v>
       </c>
       <c r="N21">
-        <v>26.4517996</v>
+        <v>26.201368</v>
       </c>
       <c r="O21">
-        <v>5.819395911999999</v>
+        <v>5.764300959999999</v>
       </c>
       <c r="P21">
-        <v>20.632403688</v>
+        <v>20.43706704</v>
       </c>
       <c r="Q21">
-        <v>21.022403688</v>
+        <v>20.82706704</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1001760921428528</v>
+        <v>0.1007293867560784</v>
       </c>
       <c r="T21">
-        <v>0.7087027656745593</v>
+        <v>0.7159140492952303</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.559202508578664</v>
+        <v>6.231242383149729</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08905430940486272</v>
+        <v>0.08908252417401474</v>
       </c>
       <c r="C22">
-        <v>418.0185727019448</v>
+        <v>413.0884850037972</v>
       </c>
       <c r="D22">
-        <v>487.9585727019448</v>
+        <v>487.6404850037972</v>
       </c>
       <c r="E22">
-        <v>-163.36</v>
+        <v>-158.748</v>
       </c>
       <c r="F22">
-        <v>92.24000000000001</v>
+        <v>96.852</v>
       </c>
       <c r="G22">
         <v>22.3</v>
@@ -3085,45 +3085,45 @@
         <v>31.21</v>
       </c>
       <c r="M22">
-        <v>5.008632</v>
+        <v>5.3559156</v>
       </c>
       <c r="N22">
-        <v>26.201368</v>
+        <v>25.8540844</v>
       </c>
       <c r="O22">
-        <v>5.764300959999999</v>
+        <v>5.687898568</v>
       </c>
       <c r="P22">
-        <v>20.43706704</v>
+        <v>20.166185832</v>
       </c>
       <c r="Q22">
-        <v>20.82706704</v>
+        <v>20.556185832</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1007293867560784</v>
+        <v>0.1012966888278667</v>
       </c>
       <c r="T22">
-        <v>0.7159140492952303</v>
+        <v>0.7233078970581969</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.231242383149729</v>
+        <v>5.827201608628783</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08908252417401472</v>
+        <v>0.08895473894316672</v>
       </c>
       <c r="C23">
-        <v>413.0884850037975</v>
+        <v>409.9204342309984</v>
       </c>
       <c r="D23">
-        <v>487.6404850037975</v>
+        <v>489.0844342309983</v>
       </c>
       <c r="E23">
-        <v>-158.748</v>
+        <v>-154.136</v>
       </c>
       <c r="F23">
-        <v>96.85199999999999</v>
+        <v>101.464</v>
       </c>
       <c r="G23">
         <v>22.3</v>
@@ -3167,28 +3167,28 @@
         <v>31.21</v>
       </c>
       <c r="M23">
-        <v>5.355915599999999</v>
+        <v>5.6109592</v>
       </c>
       <c r="N23">
-        <v>25.8540844</v>
+        <v>25.5990408</v>
       </c>
       <c r="O23">
-        <v>5.687898568</v>
+        <v>5.631788975999999</v>
       </c>
       <c r="P23">
-        <v>20.166185832</v>
+        <v>19.967251824</v>
       </c>
       <c r="Q23">
-        <v>20.556185832</v>
+        <v>20.357251824</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1012966888278667</v>
+        <v>0.101878537106624</v>
       </c>
       <c r="T23">
-        <v>0.7233078970581966</v>
+        <v>0.7308913306612392</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.827201608628784</v>
+        <v>5.562328808236567</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08895473894316672</v>
+        <v>0.08882695371231869</v>
       </c>
       <c r="C24">
-        <v>409.9204342309984</v>
+        <v>406.760960192986</v>
       </c>
       <c r="D24">
-        <v>489.0844342309983</v>
+        <v>490.536960192986</v>
       </c>
       <c r="E24">
-        <v>-154.136</v>
+        <v>-149.524</v>
       </c>
       <c r="F24">
-        <v>101.464</v>
+        <v>106.076</v>
       </c>
       <c r="G24">
         <v>22.3</v>
@@ -3249,28 +3249,28 @@
         <v>31.21</v>
       </c>
       <c r="M24">
-        <v>5.6109592</v>
+        <v>5.8660028</v>
       </c>
       <c r="N24">
-        <v>25.5990408</v>
+        <v>25.3439972</v>
       </c>
       <c r="O24">
-        <v>5.631788975999999</v>
+        <v>5.575679383999999</v>
       </c>
       <c r="P24">
-        <v>19.967251824</v>
+        <v>19.768317816</v>
       </c>
       <c r="Q24">
-        <v>20.357251824</v>
+        <v>20.158317816</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.101878537106624</v>
+        <v>0.1024754983276866</v>
       </c>
       <c r="T24">
-        <v>0.7308913306612392</v>
+        <v>0.7386717365656595</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.562328808236567</v>
+        <v>5.320488425269759</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08882695371231869</v>
+        <v>0.08869916848147069</v>
       </c>
       <c r="C25">
-        <v>406.760960192986</v>
+        <v>403.6101395332058</v>
       </c>
       <c r="D25">
-        <v>490.536960192986</v>
+        <v>491.9981395332059</v>
       </c>
       <c r="E25">
-        <v>-149.524</v>
+        <v>-144.912</v>
       </c>
       <c r="F25">
-        <v>106.076</v>
+        <v>110.688</v>
       </c>
       <c r="G25">
         <v>22.3</v>
@@ -3331,28 +3331,28 @@
         <v>31.21</v>
       </c>
       <c r="M25">
-        <v>5.8660028</v>
+        <v>6.1210464</v>
       </c>
       <c r="N25">
-        <v>25.3439972</v>
+        <v>25.0889536</v>
       </c>
       <c r="O25">
-        <v>5.575679383999999</v>
+        <v>5.519569792</v>
       </c>
       <c r="P25">
-        <v>19.768317816</v>
+        <v>19.569383808</v>
       </c>
       <c r="Q25">
-        <v>20.158317816</v>
+        <v>19.959383808</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1024754983276866</v>
+        <v>0.1030881690545667</v>
       </c>
       <c r="T25">
-        <v>0.7386717365656595</v>
+        <v>0.7466568899938804</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.320488425269759</v>
+        <v>5.098801407550186</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08869916848147069</v>
+        <v>0.08857138325062267</v>
       </c>
       <c r="C26">
-        <v>403.6101395332058</v>
+        <v>400.4680498110347</v>
       </c>
       <c r="D26">
-        <v>491.9981395332059</v>
+        <v>493.4680498110348</v>
       </c>
       <c r="E26">
-        <v>-144.912</v>
+        <v>-140.3</v>
       </c>
       <c r="F26">
-        <v>110.688</v>
+        <v>115.3</v>
       </c>
       <c r="G26">
         <v>22.3</v>
@@ -3413,28 +3413,28 @@
         <v>31.21</v>
       </c>
       <c r="M26">
-        <v>6.1210464</v>
+        <v>6.37609</v>
       </c>
       <c r="N26">
-        <v>25.0889536</v>
+        <v>24.83391</v>
       </c>
       <c r="O26">
-        <v>5.519569792</v>
+        <v>5.463460199999999</v>
       </c>
       <c r="P26">
-        <v>19.569383808</v>
+        <v>19.3704498</v>
       </c>
       <c r="Q26">
-        <v>19.959383808</v>
+        <v>19.7604498</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1030881690545667</v>
+        <v>0.1037171776674969</v>
       </c>
       <c r="T26">
-        <v>0.7466568899938804</v>
+        <v>0.7548549808468537</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.098801407550186</v>
+        <v>4.894849351248178</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08857138325062267</v>
+        <v>0.08844359801977467</v>
       </c>
       <c r="C27">
-        <v>400.4680498110347</v>
+        <v>397.3347695155019</v>
       </c>
       <c r="D27">
-        <v>493.4680498110348</v>
+        <v>494.9467695155019</v>
       </c>
       <c r="E27">
-        <v>-140.3</v>
+        <v>-135.688</v>
       </c>
       <c r="F27">
-        <v>115.3</v>
+        <v>119.912</v>
       </c>
       <c r="G27">
         <v>22.3</v>
@@ -3495,28 +3495,28 @@
         <v>31.21</v>
       </c>
       <c r="M27">
-        <v>6.37609</v>
+        <v>6.631133600000001</v>
       </c>
       <c r="N27">
-        <v>24.83391</v>
+        <v>24.5788664</v>
       </c>
       <c r="O27">
-        <v>5.463460199999999</v>
+        <v>5.407350607999999</v>
       </c>
       <c r="P27">
-        <v>19.3704498</v>
+        <v>19.171515792</v>
       </c>
       <c r="Q27">
-        <v>19.7604498</v>
+        <v>19.561515792</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1037171776674969</v>
+        <v>0.104363186513209</v>
       </c>
       <c r="T27">
-        <v>0.7548549808468537</v>
+        <v>0.7632746417228804</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.894849351248178</v>
+        <v>4.706585914661709</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08844359801977467</v>
+        <v>0.08831581278892665</v>
       </c>
       <c r="C28">
-        <v>397.3347695155019</v>
+        <v>394.2103780792617</v>
       </c>
       <c r="D28">
-        <v>494.9467695155019</v>
+        <v>496.4343780792617</v>
       </c>
       <c r="E28">
-        <v>-135.688</v>
+        <v>-131.076</v>
       </c>
       <c r="F28">
-        <v>119.912</v>
+        <v>124.524</v>
       </c>
       <c r="G28">
         <v>22.3</v>
@@ -3577,28 +3577,28 @@
         <v>31.21</v>
       </c>
       <c r="M28">
-        <v>6.631133600000001</v>
+        <v>6.886177200000001</v>
       </c>
       <c r="N28">
-        <v>24.5788664</v>
+        <v>24.32382279999999</v>
       </c>
       <c r="O28">
-        <v>5.407350607999999</v>
+        <v>5.351241015999999</v>
       </c>
       <c r="P28">
-        <v>19.171515792</v>
+        <v>18.972581784</v>
       </c>
       <c r="Q28">
-        <v>19.561515792</v>
+        <v>19.362581784</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.104363186513209</v>
+        <v>0.1050268942314064</v>
       </c>
       <c r="T28">
-        <v>0.7632746417228804</v>
+        <v>0.7719249782393461</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.706585914661709</v>
+        <v>4.532267917822386</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08831581278892665</v>
+        <v>0.08873402755807863</v>
       </c>
       <c r="C29">
-        <v>394.2103780792617</v>
+        <v>384.7626754760835</v>
       </c>
       <c r="D29">
-        <v>496.4343780792617</v>
+        <v>491.5986754760835</v>
       </c>
       <c r="E29">
-        <v>-131.076</v>
+        <v>-126.464</v>
       </c>
       <c r="F29">
-        <v>124.524</v>
+        <v>129.136</v>
       </c>
       <c r="G29">
         <v>22.3</v>
@@ -3659,45 +3659,45 @@
         <v>31.21</v>
       </c>
       <c r="M29">
-        <v>6.886177200000001</v>
+        <v>7.4640608</v>
       </c>
       <c r="N29">
-        <v>24.32382279999999</v>
+        <v>23.7459392</v>
       </c>
       <c r="O29">
-        <v>5.351241015999999</v>
+        <v>5.224106623999999</v>
       </c>
       <c r="P29">
-        <v>18.972581784</v>
+        <v>18.52183257599999</v>
       </c>
       <c r="Q29">
-        <v>19.362581784</v>
+        <v>18.91183257599999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1050268942314064</v>
+        <v>0.1057090382751092</v>
       </c>
       <c r="T29">
-        <v>0.7719249782393461</v>
+        <v>0.7808156018812693</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.532267917822386</v>
+        <v>4.181370012420048</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08873402755807863</v>
+        <v>0.08862574232723062</v>
       </c>
       <c r="C30">
-        <v>384.7626754760835</v>
+        <v>381.3936866456681</v>
       </c>
       <c r="D30">
-        <v>491.5986754760835</v>
+        <v>492.8416866456682</v>
       </c>
       <c r="E30">
-        <v>-126.464</v>
+        <v>-121.852</v>
       </c>
       <c r="F30">
-        <v>129.136</v>
+        <v>133.748</v>
       </c>
       <c r="G30">
         <v>22.3</v>
@@ -3741,28 +3741,28 @@
         <v>31.21</v>
       </c>
       <c r="M30">
-        <v>7.4640608</v>
+        <v>7.730634400000001</v>
       </c>
       <c r="N30">
-        <v>23.7459392</v>
+        <v>23.47936559999999</v>
       </c>
       <c r="O30">
-        <v>5.224106623999999</v>
+        <v>5.165460431999999</v>
       </c>
       <c r="P30">
-        <v>18.52183257599999</v>
+        <v>18.31390516799999</v>
       </c>
       <c r="Q30">
-        <v>18.91183257599999</v>
+        <v>18.703905168</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1057090382751092</v>
+        <v>0.1064103976439868</v>
       </c>
       <c r="T30">
-        <v>0.7808156018812693</v>
+        <v>0.7899566656257818</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.181370012420048</v>
+        <v>4.037184839577977</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08862574232723061</v>
+        <v>0.0893364570963826</v>
       </c>
       <c r="C31">
-        <v>381.3936866456683</v>
+        <v>368.7362486630275</v>
       </c>
       <c r="D31">
-        <v>492.8416866456683</v>
+        <v>484.7962486630274</v>
       </c>
       <c r="E31">
-        <v>-121.852</v>
+        <v>-117.24</v>
       </c>
       <c r="F31">
-        <v>133.748</v>
+        <v>138.36</v>
       </c>
       <c r="G31">
         <v>22.3</v>
@@ -3823,45 +3823,45 @@
         <v>31.21</v>
       </c>
       <c r="M31">
-        <v>7.7306344</v>
+        <v>8.481468</v>
       </c>
       <c r="N31">
-        <v>23.4793656</v>
+        <v>22.728532</v>
       </c>
       <c r="O31">
-        <v>5.165460432</v>
+        <v>5.000277039999999</v>
       </c>
       <c r="P31">
-        <v>18.313905168</v>
+        <v>17.72825496</v>
       </c>
       <c r="Q31">
-        <v>18.703905168</v>
+        <v>18.11825496</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1064103976439868</v>
+        <v>0.1071317958519752</v>
       </c>
       <c r="T31">
-        <v>0.7899566656257818</v>
+        <v>0.7993589026201375</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.037184839577979</v>
+        <v>3.679787508483201</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0893364570963826</v>
+        <v>0.08925547186553461</v>
       </c>
       <c r="C32">
-        <v>368.7362486630275</v>
+        <v>365.027732952272</v>
       </c>
       <c r="D32">
-        <v>484.7962486630274</v>
+        <v>485.699732952272</v>
       </c>
       <c r="E32">
-        <v>-117.24</v>
+        <v>-112.628</v>
       </c>
       <c r="F32">
-        <v>138.36</v>
+        <v>142.972</v>
       </c>
       <c r="G32">
         <v>22.3</v>
@@ -3905,28 +3905,28 @@
         <v>31.21</v>
       </c>
       <c r="M32">
-        <v>8.481468</v>
+        <v>8.764183600000001</v>
       </c>
       <c r="N32">
-        <v>22.728532</v>
+        <v>22.4458164</v>
       </c>
       <c r="O32">
-        <v>5.000277039999999</v>
+        <v>4.938079608</v>
       </c>
       <c r="P32">
-        <v>17.72825496</v>
+        <v>17.507736792</v>
       </c>
       <c r="Q32">
-        <v>18.11825496</v>
+        <v>17.897736792</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1071317958519752</v>
+        <v>0.1078741041529487</v>
       </c>
       <c r="T32">
-        <v>0.7993589026201375</v>
+        <v>0.8090336682230255</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.679787508483201</v>
+        <v>3.561084685628904</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08925547186553461</v>
+        <v>0.08987336663468661</v>
       </c>
       <c r="C33">
-        <v>365.027732952272</v>
+        <v>353.6063751181568</v>
       </c>
       <c r="D33">
-        <v>485.699732952272</v>
+        <v>478.8903751181568</v>
       </c>
       <c r="E33">
-        <v>-112.628</v>
+        <v>-108.016</v>
       </c>
       <c r="F33">
-        <v>142.972</v>
+        <v>147.584</v>
       </c>
       <c r="G33">
         <v>22.3</v>
@@ -3987,45 +3987,45 @@
         <v>31.21</v>
       </c>
       <c r="M33">
-        <v>8.764183600000001</v>
+        <v>9.460134400000001</v>
       </c>
       <c r="N33">
-        <v>22.4458164</v>
+        <v>21.7498656</v>
       </c>
       <c r="O33">
-        <v>4.938079608</v>
+        <v>4.784970431999999</v>
       </c>
       <c r="P33">
-        <v>17.507736792</v>
+        <v>16.964895168</v>
       </c>
       <c r="Q33">
-        <v>17.897736792</v>
+        <v>17.354895168</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1078741041529487</v>
+        <v>0.1086382450510097</v>
       </c>
       <c r="T33">
-        <v>0.8090336682230255</v>
+        <v>0.8189929857554099</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.561084685628904</v>
+        <v>3.299107462997565</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08987336663468661</v>
+        <v>0.08981422140383857</v>
       </c>
       <c r="C34">
-        <v>353.6063751181568</v>
+        <v>349.6378962548227</v>
       </c>
       <c r="D34">
-        <v>478.8903751181568</v>
+        <v>479.5338962548227</v>
       </c>
       <c r="E34">
-        <v>-108.016</v>
+        <v>-103.404</v>
       </c>
       <c r="F34">
-        <v>147.584</v>
+        <v>152.196</v>
       </c>
       <c r="G34">
         <v>22.3</v>
@@ -4069,28 +4069,28 @@
         <v>31.21</v>
       </c>
       <c r="M34">
-        <v>9.460134400000001</v>
+        <v>9.7557636</v>
       </c>
       <c r="N34">
-        <v>21.7498656</v>
+        <v>21.4542364</v>
       </c>
       <c r="O34">
-        <v>4.784970431999999</v>
+        <v>4.719932008</v>
       </c>
       <c r="P34">
-        <v>16.964895168</v>
+        <v>16.734304392</v>
       </c>
       <c r="Q34">
-        <v>17.354895168</v>
+        <v>17.124304392</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1086382450510097</v>
+        <v>0.1094251961251322</v>
       </c>
       <c r="T34">
-        <v>0.8189929857554099</v>
+        <v>0.8292495963484625</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.299107462997565</v>
+        <v>3.199134509573397</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08981422140383857</v>
+        <v>0.08975507617299058</v>
       </c>
       <c r="C35">
-        <v>349.6378962548227</v>
+        <v>345.6711492144992</v>
       </c>
       <c r="D35">
-        <v>479.5338962548227</v>
+        <v>480.1791492144993</v>
       </c>
       <c r="E35">
-        <v>-103.404</v>
+        <v>-98.79199999999997</v>
       </c>
       <c r="F35">
-        <v>152.196</v>
+        <v>156.808</v>
       </c>
       <c r="G35">
         <v>22.3</v>
@@ -4151,28 +4151,28 @@
         <v>31.21</v>
       </c>
       <c r="M35">
-        <v>9.7557636</v>
+        <v>10.0513928</v>
       </c>
       <c r="N35">
-        <v>21.4542364</v>
+        <v>21.1586072</v>
       </c>
       <c r="O35">
-        <v>4.719932008</v>
+        <v>4.654893583999999</v>
       </c>
       <c r="P35">
-        <v>16.734304392</v>
+        <v>16.503713616</v>
       </c>
       <c r="Q35">
-        <v>17.124304392</v>
+        <v>16.893713616</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1094251961251322</v>
+        <v>0.1102359942015009</v>
       </c>
       <c r="T35">
-        <v>0.8292495963484625</v>
+        <v>0.839817013323123</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.199134509573397</v>
+        <v>3.105042318115355</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08975507617299058</v>
+        <v>0.08969593094214257</v>
       </c>
       <c r="C36">
-        <v>345.6711492144992</v>
+        <v>341.7061409975447</v>
       </c>
       <c r="D36">
-        <v>480.1791492144993</v>
+        <v>480.8261409975447</v>
       </c>
       <c r="E36">
-        <v>-98.79199999999997</v>
+        <v>-94.17999999999998</v>
       </c>
       <c r="F36">
-        <v>156.808</v>
+        <v>161.42</v>
       </c>
       <c r="G36">
         <v>22.3</v>
@@ -4233,28 +4233,28 @@
         <v>31.21</v>
       </c>
       <c r="M36">
-        <v>10.0513928</v>
+        <v>10.347022</v>
       </c>
       <c r="N36">
-        <v>21.1586072</v>
+        <v>20.862978</v>
       </c>
       <c r="O36">
-        <v>4.654893583999999</v>
+        <v>4.58985516</v>
       </c>
       <c r="P36">
-        <v>16.503713616</v>
+        <v>16.27312284</v>
       </c>
       <c r="Q36">
-        <v>16.893713616</v>
+        <v>16.66312284</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1102359942015009</v>
+        <v>0.1110717399109886</v>
       </c>
       <c r="T36">
-        <v>0.839817013323123</v>
+        <v>0.8507095815893114</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.105042318115355</v>
+        <v>3.01632682331206</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08969593094214257</v>
+        <v>0.09182702571129456</v>
       </c>
       <c r="C37">
-        <v>341.7061409975447</v>
+        <v>314.8314364643696</v>
       </c>
       <c r="D37">
-        <v>480.8261409975447</v>
+        <v>458.5634364643696</v>
       </c>
       <c r="E37">
-        <v>-94.17999999999998</v>
+        <v>-89.56799999999998</v>
       </c>
       <c r="F37">
-        <v>161.42</v>
+        <v>166.032</v>
       </c>
       <c r="G37">
         <v>22.3</v>
@@ -4315,45 +4315,45 @@
         <v>31.21</v>
       </c>
       <c r="M37">
-        <v>10.347022</v>
+        <v>11.9377008</v>
       </c>
       <c r="N37">
-        <v>20.862978</v>
+        <v>19.2722992</v>
       </c>
       <c r="O37">
-        <v>4.58985516</v>
+        <v>4.239905823999999</v>
       </c>
       <c r="P37">
-        <v>16.27312284</v>
+        <v>15.032393376</v>
       </c>
       <c r="Q37">
-        <v>16.66312284</v>
+        <v>15.422393376</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1110717399109886</v>
+        <v>0.1119336026738978</v>
       </c>
       <c r="T37">
-        <v>0.8507095815893114</v>
+        <v>0.8619425426138182</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.01632682331206</v>
+        <v>2.614406285002552</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09182702571129456</v>
+        <v>0.09182872048044655</v>
       </c>
       <c r="C38">
-        <v>314.8314364643696</v>
+        <v>310.2025522416877</v>
       </c>
       <c r="D38">
-        <v>458.5634364643696</v>
+        <v>458.5465522416877</v>
       </c>
       <c r="E38">
-        <v>-89.56800000000001</v>
+        <v>-84.95599999999999</v>
       </c>
       <c r="F38">
-        <v>166.032</v>
+        <v>170.644</v>
       </c>
       <c r="G38">
         <v>22.3</v>
@@ -4397,28 +4397,28 @@
         <v>31.21</v>
       </c>
       <c r="M38">
-        <v>11.9377008</v>
+        <v>12.2693036</v>
       </c>
       <c r="N38">
-        <v>19.2722992</v>
+        <v>18.9406964</v>
       </c>
       <c r="O38">
-        <v>4.239905824</v>
+        <v>4.166953207999999</v>
       </c>
       <c r="P38">
-        <v>15.032393376</v>
+        <v>14.773743192</v>
       </c>
       <c r="Q38">
-        <v>15.422393376</v>
+        <v>15.163743192</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1119336026738977</v>
+        <v>0.1128228261594389</v>
       </c>
       <c r="T38">
-        <v>0.861942542613818</v>
+        <v>0.8735321055756107</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.614406285002552</v>
+        <v>2.543746655678159</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09182872048044655</v>
+        <v>0.09298637524959855</v>
       </c>
       <c r="C39">
-        <v>310.2025522416877</v>
+        <v>294.3407242929874</v>
       </c>
       <c r="D39">
-        <v>458.5465522416877</v>
+        <v>447.2967242929874</v>
       </c>
       <c r="E39">
-        <v>-84.95599999999999</v>
+        <v>-80.34399999999999</v>
       </c>
       <c r="F39">
-        <v>170.644</v>
+        <v>175.256</v>
       </c>
       <c r="G39">
         <v>22.3</v>
@@ -4479,45 +4479,45 @@
         <v>31.21</v>
       </c>
       <c r="M39">
-        <v>12.2693036</v>
+        <v>13.2844048</v>
       </c>
       <c r="N39">
-        <v>18.9406964</v>
+        <v>17.9255952</v>
       </c>
       <c r="O39">
-        <v>4.166953207999999</v>
+        <v>3.943630943999999</v>
       </c>
       <c r="P39">
-        <v>14.773743192</v>
+        <v>13.981964256</v>
       </c>
       <c r="Q39">
-        <v>15.163743192</v>
+        <v>14.371964256</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1128228261594389</v>
+        <v>0.113740734273546</v>
       </c>
       <c r="T39">
-        <v>0.8735321055756107</v>
+        <v>0.8854955254071386</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.543746655678159</v>
+        <v>2.349371347070062</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09298637524959855</v>
+        <v>0.09301849001875052</v>
       </c>
       <c r="C40">
-        <v>294.3407242929874</v>
+        <v>289.4245038268649</v>
       </c>
       <c r="D40">
-        <v>447.2967242929874</v>
+        <v>446.9925038268649</v>
       </c>
       <c r="E40">
-        <v>-80.34399999999999</v>
+        <v>-75.732</v>
       </c>
       <c r="F40">
-        <v>175.256</v>
+        <v>179.868</v>
       </c>
       <c r="G40">
         <v>22.3</v>
@@ -4561,28 +4561,28 @@
         <v>31.21</v>
       </c>
       <c r="M40">
-        <v>13.2844048</v>
+        <v>13.6339944</v>
       </c>
       <c r="N40">
-        <v>17.9255952</v>
+        <v>17.57600559999999</v>
       </c>
       <c r="O40">
-        <v>3.943630943999999</v>
+        <v>3.866721231999999</v>
       </c>
       <c r="P40">
-        <v>13.981964256</v>
+        <v>13.709284368</v>
       </c>
       <c r="Q40">
-        <v>14.371964256</v>
+        <v>14.099284368</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.113740734273546</v>
+        <v>0.1146887377356566</v>
       </c>
       <c r="T40">
-        <v>0.8854955254071386</v>
+        <v>0.8978511885118314</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.349371347070062</v>
+        <v>2.289131056119547</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09301849001875052</v>
+        <v>0.09305060478790252</v>
       </c>
       <c r="C41">
-        <v>289.4245038268649</v>
+        <v>284.5086968991545</v>
       </c>
       <c r="D41">
-        <v>446.9925038268649</v>
+        <v>446.6886968991545</v>
       </c>
       <c r="E41">
-        <v>-75.732</v>
+        <v>-71.11999999999998</v>
       </c>
       <c r="F41">
-        <v>179.868</v>
+        <v>184.48</v>
       </c>
       <c r="G41">
         <v>22.3</v>
@@ -4643,28 +4643,28 @@
         <v>31.21</v>
       </c>
       <c r="M41">
-        <v>13.6339944</v>
+        <v>13.983584</v>
       </c>
       <c r="N41">
-        <v>17.57600559999999</v>
+        <v>17.22641599999999</v>
       </c>
       <c r="O41">
-        <v>3.866721231999999</v>
+        <v>3.789811519999998</v>
       </c>
       <c r="P41">
-        <v>13.709284368</v>
+        <v>13.43660447999999</v>
       </c>
       <c r="Q41">
-        <v>14.099284368</v>
+        <v>13.82660447999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1146887377356566</v>
+        <v>0.1156683413131709</v>
       </c>
       <c r="T41">
-        <v>0.8978511885118314</v>
+        <v>0.9106187070533474</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.289131056119547</v>
+        <v>2.231902779716559</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09305060478790252</v>
+        <v>0.09308271955705452</v>
       </c>
       <c r="C42">
-        <v>284.5086968991545</v>
+        <v>279.5933026672213</v>
       </c>
       <c r="D42">
-        <v>446.6886968991545</v>
+        <v>446.3853026672213</v>
       </c>
       <c r="E42">
-        <v>-71.11999999999998</v>
+        <v>-66.50799999999998</v>
       </c>
       <c r="F42">
-        <v>184.48</v>
+        <v>189.092</v>
       </c>
       <c r="G42">
         <v>22.3</v>
@@ -4725,28 +4725,28 @@
         <v>31.21</v>
       </c>
       <c r="M42">
-        <v>13.983584</v>
+        <v>14.3331736</v>
       </c>
       <c r="N42">
-        <v>17.22641599999999</v>
+        <v>16.8768264</v>
       </c>
       <c r="O42">
-        <v>3.789811519999998</v>
+        <v>3.712901807999999</v>
       </c>
       <c r="P42">
-        <v>13.43660447999999</v>
+        <v>13.163924592</v>
       </c>
       <c r="Q42">
-        <v>13.82660447999999</v>
+        <v>13.553924592</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1156683413131709</v>
+        <v>0.1166811517916178</v>
       </c>
       <c r="T42">
-        <v>0.9106187070533474</v>
+        <v>0.9238190228335587</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.231902779716559</v>
+        <v>2.17746612655274</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09308271955705452</v>
+        <v>0.09311483432620649</v>
       </c>
       <c r="C43">
-        <v>279.5933026672213</v>
+        <v>274.6783202907185</v>
       </c>
       <c r="D43">
-        <v>446.3853026672213</v>
+        <v>446.0823202907185</v>
       </c>
       <c r="E43">
-        <v>-66.50799999999998</v>
+        <v>-61.89599999999999</v>
       </c>
       <c r="F43">
-        <v>189.092</v>
+        <v>193.704</v>
       </c>
       <c r="G43">
         <v>22.3</v>
@@ -4807,28 +4807,28 @@
         <v>31.21</v>
       </c>
       <c r="M43">
-        <v>14.3331736</v>
+        <v>14.6827632</v>
       </c>
       <c r="N43">
-        <v>16.8768264</v>
+        <v>16.5272368</v>
       </c>
       <c r="O43">
-        <v>3.712901807999999</v>
+        <v>3.635992095999999</v>
       </c>
       <c r="P43">
-        <v>13.163924592</v>
+        <v>12.891244704</v>
       </c>
       <c r="Q43">
-        <v>13.553924592</v>
+        <v>13.281244704</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1166811517916178</v>
+        <v>0.1177288867693215</v>
       </c>
       <c r="T43">
-        <v>0.9238190228335587</v>
+        <v>0.9374745219165358</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.17746612655274</v>
+        <v>2.125621694968151</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0931148343262065</v>
+        <v>0.09314694909535849</v>
       </c>
       <c r="C44">
-        <v>274.6783202907184</v>
+        <v>269.7637489315782</v>
       </c>
       <c r="D44">
-        <v>446.0823202907184</v>
+        <v>445.7797489315782</v>
       </c>
       <c r="E44">
-        <v>-61.89600000000002</v>
+        <v>-57.28399999999999</v>
       </c>
       <c r="F44">
-        <v>193.704</v>
+        <v>198.316</v>
       </c>
       <c r="G44">
         <v>22.3</v>
@@ -4889,28 +4889,28 @@
         <v>31.21</v>
       </c>
       <c r="M44">
-        <v>14.6827632</v>
+        <v>15.0323528</v>
       </c>
       <c r="N44">
-        <v>16.5272368</v>
+        <v>16.1776472</v>
       </c>
       <c r="O44">
-        <v>3.635992095999999</v>
+        <v>3.559082383999999</v>
       </c>
       <c r="P44">
-        <v>12.891244704</v>
+        <v>12.618564816</v>
       </c>
       <c r="Q44">
-        <v>13.281244704</v>
+        <v>13.008564816</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1177288867693215</v>
+        <v>0.1188133843778219</v>
       </c>
       <c r="T44">
-        <v>0.9374745219165358</v>
+        <v>0.951609161318214</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.125621694968151</v>
+        <v>2.076188632294473</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09314694909535849</v>
+        <v>0.09317906386451048</v>
       </c>
       <c r="C45">
-        <v>269.7637489315782</v>
+        <v>264.8495877540061</v>
       </c>
       <c r="D45">
-        <v>445.7797489315782</v>
+        <v>445.477587754006</v>
       </c>
       <c r="E45">
-        <v>-57.28399999999999</v>
+        <v>-52.672</v>
       </c>
       <c r="F45">
-        <v>198.316</v>
+        <v>202.928</v>
       </c>
       <c r="G45">
         <v>22.3</v>
@@ -4971,28 +4971,28 @@
         <v>31.21</v>
       </c>
       <c r="M45">
-        <v>15.0323528</v>
+        <v>15.3819424</v>
       </c>
       <c r="N45">
-        <v>16.1776472</v>
+        <v>15.8280576</v>
       </c>
       <c r="O45">
-        <v>3.559082383999999</v>
+        <v>3.482172671999999</v>
       </c>
       <c r="P45">
-        <v>12.618564816</v>
+        <v>12.345884928</v>
       </c>
       <c r="Q45">
-        <v>13.008564816</v>
+        <v>12.735884928</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1188133843778219</v>
+        <v>0.1199366140437687</v>
       </c>
       <c r="T45">
-        <v>0.951609161318214</v>
+        <v>0.9662486092699523</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.076188632294473</v>
+        <v>2.029002527015053</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09317906386451048</v>
+        <v>0.09819537863366246</v>
       </c>
       <c r="C46">
-        <v>264.8495877540061</v>
+        <v>217.587723184826</v>
       </c>
       <c r="D46">
-        <v>445.477587754006</v>
+        <v>402.827723184826</v>
       </c>
       <c r="E46">
-        <v>-52.672</v>
+        <v>-48.06</v>
       </c>
       <c r="F46">
-        <v>202.928</v>
+        <v>207.54</v>
       </c>
       <c r="G46">
         <v>22.3</v>
@@ -5053,45 +5053,45 @@
         <v>31.21</v>
       </c>
       <c r="M46">
-        <v>15.3819424</v>
+        <v>18.6786</v>
       </c>
       <c r="N46">
-        <v>15.8280576</v>
+        <v>12.5314</v>
       </c>
       <c r="O46">
-        <v>3.482172671999999</v>
+        <v>2.756908</v>
       </c>
       <c r="P46">
-        <v>12.345884928</v>
+        <v>9.774491999999999</v>
       </c>
       <c r="Q46">
-        <v>12.735884928</v>
+        <v>10.164492</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1199366140437687</v>
+        <v>0.1211006884248408</v>
       </c>
       <c r="T46">
-        <v>0.9662486092699523</v>
+        <v>0.9814204007835716</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.029002527015053</v>
+        <v>1.670896105703854</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09819537863366246</v>
+        <v>0.09833825340281446</v>
       </c>
       <c r="C47">
-        <v>217.587723184826</v>
+        <v>211.8802562777556</v>
       </c>
       <c r="D47">
-        <v>402.827723184826</v>
+        <v>401.7322562777556</v>
       </c>
       <c r="E47">
-        <v>-48.06</v>
+        <v>-43.44799999999998</v>
       </c>
       <c r="F47">
-        <v>207.54</v>
+        <v>212.152</v>
       </c>
       <c r="G47">
         <v>22.3</v>
@@ -5135,28 +5135,28 @@
         <v>31.21</v>
       </c>
       <c r="M47">
-        <v>18.6786</v>
+        <v>19.09368</v>
       </c>
       <c r="N47">
-        <v>12.5314</v>
+        <v>12.11632</v>
       </c>
       <c r="O47">
-        <v>2.756908</v>
+        <v>2.6655904</v>
       </c>
       <c r="P47">
-        <v>9.774491999999999</v>
+        <v>9.450729599999999</v>
       </c>
       <c r="Q47">
-        <v>10.164492</v>
+        <v>9.8407296</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1211006884248408</v>
+        <v>0.1223078766718786</v>
       </c>
       <c r="T47">
-        <v>0.9814204007835716</v>
+        <v>0.9971541105013992</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.670896105703854</v>
+        <v>1.634572277318987</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09833825340281446</v>
+        <v>0.09848112817196647</v>
       </c>
       <c r="C48">
-        <v>211.8802562777556</v>
+        <v>206.1787313308099</v>
       </c>
       <c r="D48">
-        <v>401.7322562777556</v>
+        <v>400.6427313308099</v>
       </c>
       <c r="E48">
-        <v>-43.44799999999998</v>
+        <v>-38.83599999999998</v>
       </c>
       <c r="F48">
-        <v>212.152</v>
+        <v>216.764</v>
       </c>
       <c r="G48">
         <v>22.3</v>
@@ -5217,28 +5217,28 @@
         <v>31.21</v>
       </c>
       <c r="M48">
-        <v>19.09368</v>
+        <v>19.50876</v>
       </c>
       <c r="N48">
-        <v>12.11632</v>
+        <v>11.70124</v>
       </c>
       <c r="O48">
-        <v>2.6655904</v>
+        <v>2.5742728</v>
       </c>
       <c r="P48">
-        <v>9.450729599999999</v>
+        <v>9.126967199999999</v>
       </c>
       <c r="Q48">
-        <v>9.8407296</v>
+        <v>9.5169672</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1223078766718786</v>
+        <v>0.1235606191923895</v>
       </c>
       <c r="T48">
-        <v>0.9971541105013992</v>
+        <v>1.013481545114239</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.634572277318987</v>
+        <v>1.599794143759009</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09848112817196647</v>
+        <v>0.09862400294111844</v>
       </c>
       <c r="C49">
-        <v>206.1787313308099</v>
+        <v>200.4831001297609</v>
       </c>
       <c r="D49">
-        <v>400.6427313308099</v>
+        <v>399.5591001297609</v>
       </c>
       <c r="E49">
-        <v>-38.83599999999998</v>
+        <v>-34.22399999999999</v>
       </c>
       <c r="F49">
-        <v>216.764</v>
+        <v>221.376</v>
       </c>
       <c r="G49">
         <v>22.3</v>
@@ -5299,28 +5299,28 @@
         <v>31.21</v>
       </c>
       <c r="M49">
-        <v>19.50876</v>
+        <v>19.92384</v>
       </c>
       <c r="N49">
-        <v>11.70124</v>
+        <v>11.28616</v>
       </c>
       <c r="O49">
-        <v>2.5742728</v>
+        <v>2.4829552</v>
       </c>
       <c r="P49">
-        <v>9.126967199999999</v>
+        <v>8.8032048</v>
       </c>
       <c r="Q49">
-        <v>9.5169672</v>
+        <v>9.1932048</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1235606191923895</v>
+        <v>0.1248615441175354</v>
       </c>
       <c r="T49">
-        <v>1.013481545114239</v>
+        <v>1.030436957981419</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.599794143759009</v>
+        <v>1.566465099097363</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09862400294111842</v>
+        <v>0.09876687771027043</v>
       </c>
       <c r="C50">
-        <v>200.4831001297611</v>
+        <v>194.7933149805988</v>
       </c>
       <c r="D50">
-        <v>399.559100129761</v>
+        <v>398.4813149805988</v>
       </c>
       <c r="E50">
-        <v>-34.22400000000002</v>
+        <v>-29.61199999999999</v>
       </c>
       <c r="F50">
-        <v>221.376</v>
+        <v>225.988</v>
       </c>
       <c r="G50">
         <v>22.3</v>
@@ -5381,28 +5381,28 @@
         <v>31.21</v>
       </c>
       <c r="M50">
-        <v>19.92384</v>
+        <v>20.33892</v>
       </c>
       <c r="N50">
-        <v>11.28616</v>
+        <v>10.87108</v>
       </c>
       <c r="O50">
-        <v>2.4829552</v>
+        <v>2.3916376</v>
       </c>
       <c r="P50">
-        <v>8.8032048</v>
+        <v>8.4794424</v>
       </c>
       <c r="Q50">
-        <v>9.1932048</v>
+        <v>8.869442400000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1248615441175354</v>
+        <v>0.1262134857064126</v>
       </c>
       <c r="T50">
-        <v>1.030436957981419</v>
+        <v>1.048057289000254</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.566465099097363</v>
+        <v>1.53449642360558</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09876687771027043</v>
+        <v>0.09890975247942241</v>
       </c>
       <c r="C51">
-        <v>194.7933149805988</v>
+        <v>189.1093287025364</v>
       </c>
       <c r="D51">
-        <v>398.4813149805988</v>
+        <v>397.4093287025364</v>
       </c>
       <c r="E51">
-        <v>-29.61199999999999</v>
+        <v>-25</v>
       </c>
       <c r="F51">
-        <v>225.988</v>
+        <v>230.6</v>
       </c>
       <c r="G51">
         <v>22.3</v>
@@ -5463,28 +5463,28 @@
         <v>31.21</v>
       </c>
       <c r="M51">
-        <v>20.33892</v>
+        <v>20.754</v>
       </c>
       <c r="N51">
-        <v>10.87108</v>
+        <v>10.456</v>
       </c>
       <c r="O51">
-        <v>2.3916376</v>
+        <v>2.30032</v>
       </c>
       <c r="P51">
-        <v>8.4794424</v>
+        <v>8.15568</v>
       </c>
       <c r="Q51">
-        <v>8.869442400000001</v>
+        <v>8.545680000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1262134857064126</v>
+        <v>0.1276195049588448</v>
       </c>
       <c r="T51">
-        <v>1.048057289000254</v>
+        <v>1.066382433259841</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.53449642360558</v>
+        <v>1.503806495133468</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09890975247942241</v>
+        <v>0.1237266982120316</v>
       </c>
       <c r="C52">
-        <v>189.1093287025364</v>
+        <v>57.93626593033275</v>
       </c>
       <c r="D52">
-        <v>397.4093287025364</v>
+        <v>270.8482659303327</v>
       </c>
       <c r="E52">
-        <v>-25</v>
+        <v>-20.38800000000001</v>
       </c>
       <c r="F52">
-        <v>230.6</v>
+        <v>235.212</v>
       </c>
       <c r="G52">
         <v>22.3</v>
@@ -5545,45 +5545,45 @@
         <v>31.21</v>
       </c>
       <c r="M52">
-        <v>20.754</v>
+        <v>34.5291216</v>
       </c>
       <c r="N52">
-        <v>10.456</v>
+        <v>-3.319121600000006</v>
       </c>
       <c r="O52">
-        <v>2.30032</v>
+        <v>-0.7302067520000014</v>
       </c>
       <c r="P52">
-        <v>8.15568</v>
+        <v>-2.588914848000005</v>
       </c>
       <c r="Q52">
-        <v>8.545680000000001</v>
+        <v>-2.198914848000005</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1276195049588448</v>
+        <v>0.1300946581915366</v>
       </c>
       <c r="T52">
-        <v>1.066382433259841</v>
+        <v>1.098641977341616</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.22</v>
+        <v>0.198852437647878</v>
       </c>
       <c r="W52">
-        <v>0.0702</v>
+        <v>0.1176084621532915</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.503806495133468</v>
+        <v>0.9038747165812638</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1237266982120316</v>
+        <v>0.1247366982120316</v>
       </c>
       <c r="C53">
-        <v>57.93626593033275</v>
+        <v>49.85874539570324</v>
       </c>
       <c r="D53">
-        <v>270.8482659303327</v>
+        <v>267.3827453957032</v>
       </c>
       <c r="E53">
-        <v>-20.38800000000001</v>
+        <v>-15.77599999999998</v>
       </c>
       <c r="F53">
-        <v>235.212</v>
+        <v>239.824</v>
       </c>
       <c r="G53">
         <v>22.3</v>
@@ -5627,37 +5627,37 @@
         <v>31.21</v>
       </c>
       <c r="M53">
-        <v>34.5291216</v>
+        <v>35.20616320000001</v>
       </c>
       <c r="N53">
-        <v>-3.319121600000006</v>
+        <v>-3.996163200000009</v>
       </c>
       <c r="O53">
-        <v>-0.7302067520000014</v>
+        <v>-0.8791559040000019</v>
       </c>
       <c r="P53">
-        <v>-2.588914848000005</v>
+        <v>-3.117007296000007</v>
       </c>
       <c r="Q53">
-        <v>-2.198914848000005</v>
+        <v>-2.727007296000007</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1300946581915366</v>
+        <v>0.1318507969038603</v>
       </c>
       <c r="T53">
-        <v>1.098641977341616</v>
+        <v>1.121530351869567</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.198852437647878</v>
+        <v>0.1950283523084957</v>
       </c>
       <c r="W53">
-        <v>0.1176084621532915</v>
+        <v>0.1181698378811128</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9038747165812638</v>
+        <v>0.8864925104931625</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1247366982120316</v>
+        <v>0.1257466982120316</v>
       </c>
       <c r="C54">
-        <v>49.85874539570324</v>
+        <v>41.86878759520201</v>
       </c>
       <c r="D54">
-        <v>267.3827453957032</v>
+        <v>264.004787595202</v>
       </c>
       <c r="E54">
-        <v>-15.77599999999998</v>
+        <v>-11.16399999999999</v>
       </c>
       <c r="F54">
-        <v>239.824</v>
+        <v>244.436</v>
       </c>
       <c r="G54">
         <v>22.3</v>
@@ -5709,37 +5709,37 @@
         <v>31.21</v>
       </c>
       <c r="M54">
-        <v>35.20616320000001</v>
+        <v>35.8832048</v>
       </c>
       <c r="N54">
-        <v>-3.996163200000009</v>
+        <v>-4.673204800000004</v>
       </c>
       <c r="O54">
-        <v>-0.8791559040000019</v>
+        <v>-1.028105056000001</v>
       </c>
       <c r="P54">
-        <v>-3.117007296000007</v>
+        <v>-3.645099744000003</v>
       </c>
       <c r="Q54">
-        <v>-2.727007296000007</v>
+        <v>-3.255099744000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1318507969038603</v>
+        <v>0.1336816649230914</v>
       </c>
       <c r="T54">
-        <v>1.121530351869567</v>
+        <v>1.145392699781685</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1950283523084957</v>
+        <v>0.19134857207626</v>
       </c>
       <c r="W54">
-        <v>0.1181698378811128</v>
+        <v>0.118710029619205</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8864925104931625</v>
+        <v>0.8697662367102728</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1257466982120316</v>
+        <v>0.1267566982120316</v>
       </c>
       <c r="C55">
-        <v>41.86878759520201</v>
+        <v>33.96311528197612</v>
       </c>
       <c r="D55">
-        <v>264.004787595202</v>
+        <v>260.7111152819761</v>
       </c>
       <c r="E55">
-        <v>-11.16399999999999</v>
+        <v>-6.551999999999992</v>
       </c>
       <c r="F55">
-        <v>244.436</v>
+        <v>249.048</v>
       </c>
       <c r="G55">
         <v>22.3</v>
@@ -5791,37 +5791,37 @@
         <v>31.21</v>
       </c>
       <c r="M55">
-        <v>35.8832048</v>
+        <v>36.5602464</v>
       </c>
       <c r="N55">
-        <v>-4.673204800000004</v>
+        <v>-5.350246400000007</v>
       </c>
       <c r="O55">
-        <v>-1.028105056000001</v>
+        <v>-1.177054208000001</v>
       </c>
       <c r="P55">
-        <v>-3.645099744000003</v>
+        <v>-4.173192192000005</v>
       </c>
       <c r="Q55">
-        <v>-3.255099744000003</v>
+        <v>-3.783192192000005</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1336816649230914</v>
+        <v>0.1355921358996803</v>
       </c>
       <c r="T55">
-        <v>1.145392699781685</v>
+        <v>1.170292541081287</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.19134857207626</v>
+        <v>0.1878050800007737</v>
       </c>
       <c r="W55">
-        <v>0.118710029619205</v>
+        <v>0.1192302142558864</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8697662367102728</v>
+        <v>0.8536594545489713</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1267566982120316</v>
+        <v>0.1277666982120316</v>
       </c>
       <c r="C56">
-        <v>33.96311528197612</v>
+        <v>26.13861273913062</v>
       </c>
       <c r="D56">
-        <v>260.7111152819761</v>
+        <v>257.4986127391306</v>
       </c>
       <c r="E56">
-        <v>-6.551999999999992</v>
+        <v>-1.939999999999969</v>
       </c>
       <c r="F56">
-        <v>249.048</v>
+        <v>253.66</v>
       </c>
       <c r="G56">
         <v>22.3</v>
@@ -5873,37 +5873,37 @@
         <v>31.21</v>
       </c>
       <c r="M56">
-        <v>36.5602464</v>
+        <v>37.23728800000001</v>
       </c>
       <c r="N56">
-        <v>-5.350246400000007</v>
+        <v>-6.027288000000009</v>
       </c>
       <c r="O56">
-        <v>-1.177054208000001</v>
+        <v>-1.326003360000002</v>
       </c>
       <c r="P56">
-        <v>-4.173192192000005</v>
+        <v>-4.701284640000007</v>
       </c>
       <c r="Q56">
-        <v>-3.783192192000005</v>
+        <v>-4.311284640000007</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1355921358996803</v>
+        <v>0.137587516697451</v>
       </c>
       <c r="T56">
-        <v>1.170292541081287</v>
+        <v>1.196299041994204</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1878050800007737</v>
+        <v>0.1843904421825778</v>
       </c>
       <c r="W56">
-        <v>0.1192302142558864</v>
+        <v>0.1197314830875976</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8536594545489713</v>
+        <v>0.8381383735571718</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1277666982120316</v>
+        <v>0.1287766982120316</v>
       </c>
       <c r="C57">
-        <v>26.13861273913062</v>
+        <v>18.39231594894079</v>
       </c>
       <c r="D57">
-        <v>257.4986127391306</v>
+        <v>254.3643159489408</v>
       </c>
       <c r="E57">
-        <v>-1.939999999999969</v>
+        <v>2.671999999999997</v>
       </c>
       <c r="F57">
-        <v>253.66</v>
+        <v>258.272</v>
       </c>
       <c r="G57">
         <v>22.3</v>
@@ -5955,37 +5955,37 @@
         <v>31.21</v>
       </c>
       <c r="M57">
-        <v>37.23728800000001</v>
+        <v>37.9143296</v>
       </c>
       <c r="N57">
-        <v>-6.027288000000009</v>
+        <v>-6.704329600000005</v>
       </c>
       <c r="O57">
-        <v>-1.326003360000002</v>
+        <v>-1.474952512000001</v>
       </c>
       <c r="P57">
-        <v>-4.701284640000007</v>
+        <v>-5.229377088000003</v>
       </c>
       <c r="Q57">
-        <v>-4.311284640000007</v>
+        <v>-4.839377088000004</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.137587516697451</v>
+        <v>0.1396735966223931</v>
       </c>
       <c r="T57">
-        <v>1.196299041994204</v>
+        <v>1.223487656584981</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1843904421825778</v>
+        <v>0.1810977557150318</v>
       </c>
       <c r="W57">
-        <v>0.1197314830875976</v>
+        <v>0.1202148494610333</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8381383735571718</v>
+        <v>0.8231716168865082</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1287766982120316</v>
+        <v>0.1297866982120316</v>
       </c>
       <c r="C58">
-        <v>18.39231594894079</v>
+        <v>10.72140347139759</v>
       </c>
       <c r="D58">
-        <v>254.3643159489408</v>
+        <v>251.3054034713976</v>
       </c>
       <c r="E58">
-        <v>2.671999999999997</v>
+        <v>7.28400000000002</v>
       </c>
       <c r="F58">
-        <v>258.272</v>
+        <v>262.884</v>
       </c>
       <c r="G58">
         <v>22.3</v>
@@ -6037,37 +6037,37 @@
         <v>31.21</v>
       </c>
       <c r="M58">
-        <v>37.9143296</v>
+        <v>38.5913712</v>
       </c>
       <c r="N58">
-        <v>-6.704329600000005</v>
+        <v>-7.381371200000007</v>
       </c>
       <c r="O58">
-        <v>-1.474952512000001</v>
+        <v>-1.623901664000002</v>
       </c>
       <c r="P58">
-        <v>-5.229377088000003</v>
+        <v>-5.757469536000006</v>
       </c>
       <c r="Q58">
-        <v>-4.839377088000004</v>
+        <v>-5.367469536000006</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1396735966223931</v>
+        <v>0.1418567035205883</v>
       </c>
       <c r="T58">
-        <v>1.223487656584981</v>
+        <v>1.251940857900911</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1810977557150318</v>
+        <v>0.1779206021059961</v>
       </c>
       <c r="W58">
-        <v>0.1202148494610333</v>
+        <v>0.1206812556108398</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8231716168865082</v>
+        <v>0.8087300095727097</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1297866982120316</v>
+        <v>0.1633703242151709</v>
       </c>
       <c r="C59">
-        <v>10.72140347139759</v>
+        <v>-65.67526446322057</v>
       </c>
       <c r="D59">
-        <v>251.3054034713976</v>
+        <v>179.5207355367795</v>
       </c>
       <c r="E59">
-        <v>7.28400000000002</v>
+        <v>11.89600000000004</v>
       </c>
       <c r="F59">
-        <v>262.884</v>
+        <v>267.496</v>
       </c>
       <c r="G59">
         <v>22.3</v>
@@ -6119,45 +6119,45 @@
         <v>31.21</v>
       </c>
       <c r="M59">
-        <v>38.5913712</v>
+        <v>53.71319680000001</v>
       </c>
       <c r="N59">
-        <v>-7.381371200000007</v>
+        <v>-22.50319680000001</v>
       </c>
       <c r="O59">
-        <v>-1.623901664000002</v>
+        <v>-4.950703296000002</v>
       </c>
       <c r="P59">
-        <v>-5.757469536000006</v>
+        <v>-17.552493504</v>
       </c>
       <c r="Q59">
-        <v>-5.367469536000006</v>
+        <v>-17.162493504</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1418567035205883</v>
+        <v>0.1471285917071245</v>
       </c>
       <c r="T59">
-        <v>1.251940857900911</v>
+        <v>1.320651233929954</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1779206021059961</v>
+        <v>0.1278307829185099</v>
       </c>
       <c r="W59">
-        <v>0.1206812556108398</v>
+        <v>0.1751315787899632</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8087300095727097</v>
+        <v>0.5810490132659539</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1633703242151709</v>
+        <v>0.1649203242151709</v>
       </c>
       <c r="C60">
-        <v>-65.67526446322051</v>
+        <v>-72.62319783072363</v>
       </c>
       <c r="D60">
-        <v>179.5207355367795</v>
+        <v>177.1848021692764</v>
       </c>
       <c r="E60">
-        <v>11.89599999999999</v>
+        <v>16.50800000000001</v>
       </c>
       <c r="F60">
-        <v>267.496</v>
+        <v>272.108</v>
       </c>
       <c r="G60">
         <v>22.3</v>
@@ -6201,37 +6201,37 @@
         <v>31.21</v>
       </c>
       <c r="M60">
-        <v>53.7131968</v>
+        <v>54.6392864</v>
       </c>
       <c r="N60">
-        <v>-22.5031968</v>
+        <v>-23.42928640000001</v>
       </c>
       <c r="O60">
-        <v>-4.950703296</v>
+        <v>-5.154443008000001</v>
       </c>
       <c r="P60">
-        <v>-17.552493504</v>
+        <v>-18.274843392</v>
       </c>
       <c r="Q60">
-        <v>-17.162493504</v>
+        <v>-17.884843392</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1471285917071245</v>
+        <v>0.1496000207731519</v>
       </c>
       <c r="T60">
-        <v>1.320651233929953</v>
+        <v>1.352862239635562</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1278307829185099</v>
+        <v>0.1256641594792131</v>
       </c>
       <c r="W60">
-        <v>0.1751315787899632</v>
+        <v>0.175566636776574</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.581049013265954</v>
+        <v>0.571200724905514</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1649203242151709</v>
+        <v>0.166470324215171</v>
       </c>
       <c r="C61">
-        <v>-72.62319783072363</v>
+        <v>-79.51112146935301</v>
       </c>
       <c r="D61">
-        <v>177.1848021692764</v>
+        <v>174.9088785306469</v>
       </c>
       <c r="E61">
-        <v>16.50800000000001</v>
+        <v>21.11999999999998</v>
       </c>
       <c r="F61">
-        <v>272.108</v>
+        <v>276.72</v>
       </c>
       <c r="G61">
         <v>22.3</v>
@@ -6283,37 +6283,37 @@
         <v>31.21</v>
       </c>
       <c r="M61">
-        <v>54.6392864</v>
+        <v>55.56537599999999</v>
       </c>
       <c r="N61">
-        <v>-23.42928640000001</v>
+        <v>-24.355376</v>
       </c>
       <c r="O61">
-        <v>-5.154443008000001</v>
+        <v>-5.358182719999999</v>
       </c>
       <c r="P61">
-        <v>-18.274843392</v>
+        <v>-18.99719328</v>
       </c>
       <c r="Q61">
-        <v>-17.884843392</v>
+        <v>-18.60719328</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1496000207731519</v>
+        <v>0.1521950212924807</v>
       </c>
       <c r="T61">
-        <v>1.352862239635562</v>
+        <v>1.386683795626451</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1256641594792131</v>
+        <v>0.1235697568212262</v>
       </c>
       <c r="W61">
-        <v>0.175566636776574</v>
+        <v>0.1759871928302978</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.571200724905514</v>
+        <v>0.5616807128237555</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.166470324215171</v>
+        <v>0.168020324215171</v>
       </c>
       <c r="C62">
-        <v>-79.51112146935301</v>
+        <v>-86.34131851197591</v>
       </c>
       <c r="D62">
-        <v>174.9088785306469</v>
+        <v>172.6906814880241</v>
       </c>
       <c r="E62">
-        <v>21.11999999999998</v>
+        <v>25.732</v>
       </c>
       <c r="F62">
-        <v>276.72</v>
+        <v>281.332</v>
       </c>
       <c r="G62">
         <v>22.3</v>
@@ -6365,37 +6365,37 @@
         <v>31.21</v>
       </c>
       <c r="M62">
-        <v>55.56537599999999</v>
+        <v>56.4914656</v>
       </c>
       <c r="N62">
-        <v>-24.355376</v>
+        <v>-25.2814656</v>
       </c>
       <c r="O62">
-        <v>-5.358182719999999</v>
+        <v>-5.561922432</v>
       </c>
       <c r="P62">
-        <v>-18.99719328</v>
+        <v>-19.719543168</v>
       </c>
       <c r="Q62">
-        <v>-18.60719328</v>
+        <v>-19.329543168</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1521950212924807</v>
+        <v>0.1549230987615187</v>
       </c>
       <c r="T62">
-        <v>1.386683795626451</v>
+        <v>1.422239790386104</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1235697568212262</v>
+        <v>0.1215440231028455</v>
       </c>
       <c r="W62">
-        <v>0.1759871928302978</v>
+        <v>0.1763939601609486</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5616807128237555</v>
+        <v>0.5524728322856611</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.168020324215171</v>
+        <v>0.169570324215171</v>
       </c>
       <c r="C63">
-        <v>-86.34131851197591</v>
+        <v>-93.11595772298017</v>
       </c>
       <c r="D63">
-        <v>172.6906814880241</v>
+        <v>170.5280422770198</v>
       </c>
       <c r="E63">
-        <v>25.732</v>
+        <v>30.34400000000002</v>
       </c>
       <c r="F63">
-        <v>281.332</v>
+        <v>285.944</v>
       </c>
       <c r="G63">
         <v>22.3</v>
@@ -6447,37 +6447,37 @@
         <v>31.21</v>
       </c>
       <c r="M63">
-        <v>56.4914656</v>
+        <v>57.4175552</v>
       </c>
       <c r="N63">
-        <v>-25.2814656</v>
+        <v>-26.20755520000001</v>
       </c>
       <c r="O63">
-        <v>-5.561922432</v>
+        <v>-5.765662144000001</v>
       </c>
       <c r="P63">
-        <v>-19.719543168</v>
+        <v>-20.441893056</v>
       </c>
       <c r="Q63">
-        <v>-19.329543168</v>
+        <v>-20.051893056</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1549230987615187</v>
+        <v>0.1577947592552429</v>
       </c>
       <c r="T63">
-        <v>1.422239790386104</v>
+        <v>1.459667153291001</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1215440231028455</v>
+        <v>0.1195836356334447</v>
       </c>
       <c r="W63">
-        <v>0.1763939601609486</v>
+        <v>0.1767876059648043</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5524728322856611</v>
+        <v>0.5435619801520215</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.169570324215171</v>
+        <v>0.1711203242151709</v>
       </c>
       <c r="C64">
-        <v>-93.11595772298017</v>
+        <v>-99.83710057099535</v>
       </c>
       <c r="D64">
-        <v>170.5280422770198</v>
+        <v>168.4188994290046</v>
       </c>
       <c r="E64">
-        <v>30.34400000000002</v>
+        <v>34.95599999999999</v>
       </c>
       <c r="F64">
-        <v>285.944</v>
+        <v>290.556</v>
       </c>
       <c r="G64">
         <v>22.3</v>
@@ -6529,37 +6529,37 @@
         <v>31.21</v>
       </c>
       <c r="M64">
-        <v>57.4175552</v>
+        <v>58.3436448</v>
       </c>
       <c r="N64">
-        <v>-26.20755520000001</v>
+        <v>-27.1336448</v>
       </c>
       <c r="O64">
-        <v>-5.765662144000001</v>
+        <v>-5.969401856</v>
       </c>
       <c r="P64">
-        <v>-20.441893056</v>
+        <v>-21.164242944</v>
       </c>
       <c r="Q64">
-        <v>-20.051893056</v>
+        <v>-20.774242944</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1577947592552429</v>
+        <v>0.1608216446405197</v>
       </c>
       <c r="T64">
-        <v>1.459667153291001</v>
+        <v>1.499117616893461</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1195836356334447</v>
+        <v>0.1176854826868821</v>
       </c>
       <c r="W64">
-        <v>0.1767876059648043</v>
+        <v>0.1771687550764741</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5435619801520215</v>
+        <v>0.5349340122131006</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1711203242151709</v>
+        <v>0.172670324215171</v>
       </c>
       <c r="C65">
-        <v>-99.83710057099535</v>
+        <v>-106.5067077831613</v>
       </c>
       <c r="D65">
-        <v>168.4188994290046</v>
+        <v>166.3612922168386</v>
       </c>
       <c r="E65">
-        <v>34.95599999999999</v>
+        <v>39.56800000000001</v>
       </c>
       <c r="F65">
-        <v>290.556</v>
+        <v>295.168</v>
       </c>
       <c r="G65">
         <v>22.3</v>
@@ -6611,37 +6611,37 @@
         <v>31.21</v>
       </c>
       <c r="M65">
-        <v>58.3436448</v>
+        <v>59.2697344</v>
       </c>
       <c r="N65">
-        <v>-27.1336448</v>
+        <v>-28.05973440000001</v>
       </c>
       <c r="O65">
-        <v>-5.969401856</v>
+        <v>-6.173141568000002</v>
       </c>
       <c r="P65">
-        <v>-21.164242944</v>
+        <v>-21.88659283200001</v>
       </c>
       <c r="Q65">
-        <v>-20.774242944</v>
+        <v>-21.496592832</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1608216446405197</v>
+        <v>0.1640166903249786</v>
       </c>
       <c r="T65">
-        <v>1.499117616893461</v>
+        <v>1.540759772918279</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1176854826868821</v>
+        <v>0.1158466470198996</v>
       </c>
       <c r="W65">
-        <v>0.1771687550764741</v>
+        <v>0.1775379932784042</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5349340122131006</v>
+        <v>0.5265756682722708</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.172670324215171</v>
+        <v>0.174220324215171</v>
       </c>
       <c r="C66">
-        <v>-106.5067077831613</v>
+        <v>-113.1266454247456</v>
       </c>
       <c r="D66">
-        <v>166.3612922168386</v>
+        <v>164.3533545752544</v>
       </c>
       <c r="E66">
-        <v>39.56800000000001</v>
+        <v>44.18000000000004</v>
       </c>
       <c r="F66">
-        <v>295.168</v>
+        <v>299.78</v>
       </c>
       <c r="G66">
         <v>22.3</v>
@@ -6693,37 +6693,37 @@
         <v>31.21</v>
       </c>
       <c r="M66">
-        <v>59.2697344</v>
+        <v>60.19582400000001</v>
       </c>
       <c r="N66">
-        <v>-28.05973440000001</v>
+        <v>-28.98582400000001</v>
       </c>
       <c r="O66">
-        <v>-6.173141568000002</v>
+        <v>-6.376881280000003</v>
       </c>
       <c r="P66">
-        <v>-21.88659283200001</v>
+        <v>-22.60894272000001</v>
       </c>
       <c r="Q66">
-        <v>-21.496592832</v>
+        <v>-22.21894272000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1640166903249786</v>
+        <v>0.1673943100485494</v>
       </c>
       <c r="T66">
-        <v>1.540759772918279</v>
+        <v>1.584781480715944</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1158466470198996</v>
+        <v>0.1140643909119011</v>
       </c>
       <c r="W66">
-        <v>0.1775379932784042</v>
+        <v>0.1778958703048903</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5265756682722708</v>
+        <v>0.518474504145005</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.174220324215171</v>
+        <v>0.175770324215171</v>
       </c>
       <c r="C67">
-        <v>-113.1266454247456</v>
+        <v>-119.6986905437367</v>
       </c>
       <c r="D67">
-        <v>164.3533545752544</v>
+        <v>162.3933094562632</v>
       </c>
       <c r="E67">
-        <v>44.18000000000004</v>
+        <v>48.792</v>
       </c>
       <c r="F67">
-        <v>299.78</v>
+        <v>304.392</v>
       </c>
       <c r="G67">
         <v>22.3</v>
@@ -6775,37 +6775,37 @@
         <v>31.21</v>
       </c>
       <c r="M67">
-        <v>60.19582400000001</v>
+        <v>61.1219136</v>
       </c>
       <c r="N67">
-        <v>-28.98582400000001</v>
+        <v>-29.9119136</v>
       </c>
       <c r="O67">
-        <v>-6.376881280000003</v>
+        <v>-6.580620992</v>
       </c>
       <c r="P67">
-        <v>-22.60894272000001</v>
+        <v>-23.331292608</v>
       </c>
       <c r="Q67">
-        <v>-22.21894272000001</v>
+        <v>-22.941292608</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1673943100485494</v>
+        <v>0.1709706132852715</v>
       </c>
       <c r="T67">
-        <v>1.584781480715944</v>
+        <v>1.631392700737002</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1140643909119011</v>
+        <v>0.1123361425647511</v>
       </c>
       <c r="W67">
-        <v>0.1778958703048903</v>
+        <v>0.178242902572998</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.518474504145005</v>
+        <v>0.5106188298397778</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.175770324215171</v>
+        <v>0.177320324215171</v>
       </c>
       <c r="C68">
-        <v>-119.6986905437367</v>
+        <v>-126.2245364162987</v>
       </c>
       <c r="D68">
-        <v>162.3933094562632</v>
+        <v>160.4794635837013</v>
       </c>
       <c r="E68">
-        <v>48.792</v>
+        <v>53.40400000000002</v>
       </c>
       <c r="F68">
-        <v>304.392</v>
+        <v>309.004</v>
       </c>
       <c r="G68">
         <v>22.3</v>
@@ -6857,37 +6857,37 @@
         <v>31.21</v>
       </c>
       <c r="M68">
-        <v>61.1219136</v>
+        <v>62.0480032</v>
       </c>
       <c r="N68">
-        <v>-29.9119136</v>
+        <v>-30.83800320000001</v>
       </c>
       <c r="O68">
-        <v>-6.580620992</v>
+        <v>-6.784360704000002</v>
       </c>
       <c r="P68">
-        <v>-23.331292608</v>
+        <v>-24.05364249600001</v>
       </c>
       <c r="Q68">
-        <v>-22.941292608</v>
+        <v>-23.663642496</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1709706132852715</v>
+        <v>0.1747636621727039</v>
       </c>
       <c r="T68">
-        <v>1.631392700737002</v>
+        <v>1.680828843183578</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1123361425647511</v>
+        <v>0.1106594837205011</v>
       </c>
       <c r="W68">
-        <v>0.178242902572998</v>
+        <v>0.1785795756689234</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5106188298397778</v>
+        <v>0.5029976532750049</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.177320324215171</v>
+        <v>0.2031761774495606</v>
       </c>
       <c r="C69">
-        <v>-126.2245364162987</v>
+        <v>-157.202238804029</v>
       </c>
       <c r="D69">
-        <v>160.4794635837013</v>
+        <v>134.113761195971</v>
       </c>
       <c r="E69">
-        <v>53.40400000000002</v>
+        <v>58.01600000000005</v>
       </c>
       <c r="F69">
-        <v>309.004</v>
+        <v>313.616</v>
       </c>
       <c r="G69">
         <v>22.3</v>
@@ -6939,45 +6939,45 @@
         <v>31.21</v>
       </c>
       <c r="M69">
-        <v>62.0480032</v>
+        <v>73.95065280000001</v>
       </c>
       <c r="N69">
-        <v>-30.83800320000001</v>
+        <v>-42.74065280000002</v>
       </c>
       <c r="O69">
-        <v>-6.784360704000002</v>
+        <v>-9.402943616000005</v>
       </c>
       <c r="P69">
-        <v>-24.05364249600001</v>
+        <v>-33.33770918400002</v>
       </c>
       <c r="Q69">
-        <v>-23.663642496</v>
+        <v>-32.94770918400002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1747636621727039</v>
+        <v>0.1803745679730685</v>
       </c>
       <c r="T69">
-        <v>1.680828843183578</v>
+        <v>1.753957755210046</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1106594837205011</v>
+        <v>0.09284840282031963</v>
       </c>
       <c r="W69">
-        <v>0.1785795756689234</v>
+        <v>0.2139063466149687</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.5029976532750049</v>
+        <v>0.4220381946378164</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2031761774495606</v>
+        <v>0.2050761774495606</v>
       </c>
       <c r="C70">
-        <v>-157.202238804029</v>
+        <v>-163.4140772127141</v>
       </c>
       <c r="D70">
-        <v>134.113761195971</v>
+        <v>132.5139227872859</v>
       </c>
       <c r="E70">
-        <v>58.01600000000005</v>
+        <v>62.62800000000001</v>
       </c>
       <c r="F70">
-        <v>313.616</v>
+        <v>318.228</v>
       </c>
       <c r="G70">
         <v>22.3</v>
@@ -7021,37 +7021,37 @@
         <v>31.21</v>
       </c>
       <c r="M70">
-        <v>73.95065280000001</v>
+        <v>75.0381624</v>
       </c>
       <c r="N70">
-        <v>-42.74065280000002</v>
+        <v>-43.82816240000001</v>
       </c>
       <c r="O70">
-        <v>-9.402943616000005</v>
+        <v>-9.642195728000003</v>
       </c>
       <c r="P70">
-        <v>-33.33770918400002</v>
+        <v>-34.18596667200001</v>
       </c>
       <c r="Q70">
-        <v>-32.94770918400002</v>
+        <v>-33.79596667200001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1803745679730685</v>
+        <v>0.184715683068974</v>
       </c>
       <c r="T70">
-        <v>1.753957755210046</v>
+        <v>1.810537037636176</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09284840282031963</v>
+        <v>0.0915027737939382</v>
       </c>
       <c r="W70">
-        <v>0.2139063466149687</v>
+        <v>0.2142236459393894</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4220381946378164</v>
+        <v>0.4159216990633554</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2050761774495606</v>
+        <v>0.2069761774495606</v>
       </c>
       <c r="C71">
-        <v>-163.4140772127141</v>
+        <v>-169.5881967348416</v>
       </c>
       <c r="D71">
-        <v>132.5139227872859</v>
+        <v>130.9518032651584</v>
       </c>
       <c r="E71">
-        <v>62.62800000000001</v>
+        <v>67.24000000000004</v>
       </c>
       <c r="F71">
-        <v>318.228</v>
+        <v>322.84</v>
       </c>
       <c r="G71">
         <v>22.3</v>
@@ -7103,37 +7103,37 @@
         <v>31.21</v>
       </c>
       <c r="M71">
-        <v>75.0381624</v>
+        <v>76.12567200000001</v>
       </c>
       <c r="N71">
-        <v>-43.82816240000001</v>
+        <v>-44.91567200000001</v>
       </c>
       <c r="O71">
-        <v>-9.642195728000003</v>
+        <v>-9.881447840000003</v>
       </c>
       <c r="P71">
-        <v>-34.18596667200001</v>
+        <v>-35.03422416000001</v>
       </c>
       <c r="Q71">
-        <v>-33.79596667200001</v>
+        <v>-34.64422416000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.184715683068974</v>
+        <v>0.1893462058379397</v>
       </c>
       <c r="T71">
-        <v>1.810537037636176</v>
+        <v>1.870888272224049</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0915027737939382</v>
+        <v>0.09019559131116765</v>
       </c>
       <c r="W71">
-        <v>0.2142236459393894</v>
+        <v>0.2145318795688267</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4159216990633554</v>
+        <v>0.4099799605053075</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2069761774495606</v>
+        <v>0.2088761774495606</v>
       </c>
       <c r="C72">
-        <v>-169.5881967348416</v>
+        <v>-175.7259157582763</v>
       </c>
       <c r="D72">
-        <v>130.9518032651584</v>
+        <v>129.4260842417238</v>
       </c>
       <c r="E72">
-        <v>67.24000000000004</v>
+        <v>71.85200000000006</v>
       </c>
       <c r="F72">
-        <v>322.84</v>
+        <v>327.4520000000001</v>
       </c>
       <c r="G72">
         <v>22.3</v>
@@ -7185,37 +7185,37 @@
         <v>31.21</v>
       </c>
       <c r="M72">
-        <v>76.12567200000001</v>
+        <v>77.21318160000001</v>
       </c>
       <c r="N72">
-        <v>-44.91567200000001</v>
+        <v>-46.00318160000002</v>
       </c>
       <c r="O72">
-        <v>-9.881447840000003</v>
+        <v>-10.120699952</v>
       </c>
       <c r="P72">
-        <v>-35.03422416000001</v>
+        <v>-35.88248164800002</v>
       </c>
       <c r="Q72">
-        <v>-34.64422416000001</v>
+        <v>-35.49248164800002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1893462058379397</v>
+        <v>0.1942960750047653</v>
       </c>
       <c r="T72">
-        <v>1.870888272224049</v>
+        <v>1.93540166092143</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09019559131116765</v>
+        <v>0.08892523087016529</v>
       </c>
       <c r="W72">
-        <v>0.2145318795688267</v>
+        <v>0.214831430560815</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4099799605053075</v>
+        <v>0.4042055948643876</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2088761774495606</v>
+        <v>0.2107761774495606</v>
       </c>
       <c r="C73">
-        <v>-175.7259157582762</v>
+        <v>-181.8284919363699</v>
       </c>
       <c r="D73">
-        <v>129.4260842417238</v>
+        <v>127.9355080636301</v>
       </c>
       <c r="E73">
-        <v>71.852</v>
+        <v>76.46399999999997</v>
       </c>
       <c r="F73">
-        <v>327.452</v>
+        <v>332.064</v>
       </c>
       <c r="G73">
         <v>22.3</v>
@@ -7267,37 +7267,37 @@
         <v>31.21</v>
       </c>
       <c r="M73">
-        <v>77.2131816</v>
+        <v>78.30069119999999</v>
       </c>
       <c r="N73">
-        <v>-46.0031816</v>
+        <v>-47.09069119999999</v>
       </c>
       <c r="O73">
-        <v>-10.120699952</v>
+        <v>-10.359952064</v>
       </c>
       <c r="P73">
-        <v>-35.882481648</v>
+        <v>-36.730739136</v>
       </c>
       <c r="Q73">
-        <v>-35.492481648</v>
+        <v>-36.340739136</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1942960750047652</v>
+        <v>0.1995995062549354</v>
       </c>
       <c r="T73">
-        <v>1.935401660921429</v>
+        <v>2.00452314881148</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08892523087016529</v>
+        <v>0.08769015821919079</v>
       </c>
       <c r="W73">
-        <v>0.214831430560815</v>
+        <v>0.2151226606919148</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4042055948643877</v>
+        <v>0.398591628269049</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2107761774495606</v>
+        <v>0.2126761774495606</v>
       </c>
       <c r="C74">
-        <v>-181.8284919363699</v>
+        <v>-187.8971256454826</v>
       </c>
       <c r="D74">
-        <v>127.9355080636301</v>
+        <v>126.4788743545174</v>
       </c>
       <c r="E74">
-        <v>76.46399999999997</v>
+        <v>81.07599999999999</v>
       </c>
       <c r="F74">
-        <v>332.064</v>
+        <v>336.676</v>
       </c>
       <c r="G74">
         <v>22.3</v>
@@ -7349,37 +7349,37 @@
         <v>31.21</v>
       </c>
       <c r="M74">
-        <v>78.30069119999999</v>
+        <v>79.38820080000001</v>
       </c>
       <c r="N74">
-        <v>-47.09069119999999</v>
+        <v>-48.17820080000001</v>
       </c>
       <c r="O74">
-        <v>-10.359952064</v>
+        <v>-10.599204176</v>
       </c>
       <c r="P74">
-        <v>-36.730739136</v>
+        <v>-37.57899662400001</v>
       </c>
       <c r="Q74">
-        <v>-36.340739136</v>
+        <v>-37.18899662400001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1995995062549354</v>
+        <v>0.2052957842643774</v>
       </c>
       <c r="T74">
-        <v>2.00452314881148</v>
+        <v>2.078764746915609</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08769015821919079</v>
+        <v>0.08648892317509227</v>
       </c>
       <c r="W74">
-        <v>0.2151226606919148</v>
+        <v>0.2154059119153132</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.398591628269049</v>
+        <v>0.3931314689776921</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2126761774495606</v>
+        <v>0.2145761774495606</v>
       </c>
       <c r="C75">
-        <v>-187.8971256454826</v>
+        <v>-193.9329632089646</v>
       </c>
       <c r="D75">
-        <v>126.4788743545174</v>
+        <v>125.0550367910354</v>
       </c>
       <c r="E75">
-        <v>81.07599999999999</v>
+        <v>85.68800000000002</v>
       </c>
       <c r="F75">
-        <v>336.676</v>
+        <v>341.288</v>
       </c>
       <c r="G75">
         <v>22.3</v>
@@ -7431,37 +7431,37 @@
         <v>31.21</v>
       </c>
       <c r="M75">
-        <v>79.38820080000001</v>
+        <v>80.47571040000001</v>
       </c>
       <c r="N75">
-        <v>-48.17820080000001</v>
+        <v>-49.26571040000002</v>
       </c>
       <c r="O75">
-        <v>-10.599204176</v>
+        <v>-10.838456288</v>
       </c>
       <c r="P75">
-        <v>-37.57899662400001</v>
+        <v>-38.42725411200001</v>
       </c>
       <c r="Q75">
-        <v>-37.18899662400001</v>
+        <v>-38.03725411200001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2052957842643774</v>
+        <v>0.211430237505315</v>
       </c>
       <c r="T75">
-        <v>2.078764746915609</v>
+        <v>2.158717237181594</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08648892317509227</v>
+        <v>0.08532015394299643</v>
       </c>
       <c r="W75">
-        <v>0.2154059119153132</v>
+        <v>0.2156815077002414</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3931314689776921</v>
+        <v>0.3878188815590746</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2145761774495606</v>
+        <v>0.2164761774495606</v>
       </c>
       <c r="C76">
-        <v>-193.9329632089646</v>
+        <v>-199.937099905799</v>
       </c>
       <c r="D76">
-        <v>125.0550367910354</v>
+        <v>123.6629000942009</v>
       </c>
       <c r="E76">
-        <v>85.68800000000002</v>
+        <v>90.29999999999998</v>
       </c>
       <c r="F76">
-        <v>341.288</v>
+        <v>345.9</v>
       </c>
       <c r="G76">
         <v>22.3</v>
@@ -7513,37 +7513,37 @@
         <v>31.21</v>
       </c>
       <c r="M76">
-        <v>80.47571040000001</v>
+        <v>81.56322</v>
       </c>
       <c r="N76">
-        <v>-49.26571040000002</v>
+        <v>-50.35322000000001</v>
       </c>
       <c r="O76">
-        <v>-10.838456288</v>
+        <v>-11.0777084</v>
       </c>
       <c r="P76">
-        <v>-38.42725411200001</v>
+        <v>-39.2755116</v>
       </c>
       <c r="Q76">
-        <v>-38.03725411200001</v>
+        <v>-38.8855116</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.211430237505315</v>
+        <v>0.2180554470055277</v>
       </c>
       <c r="T76">
-        <v>2.158717237181594</v>
+        <v>2.245065926668858</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08532015394299643</v>
+        <v>0.08418255189042315</v>
       </c>
       <c r="W76">
-        <v>0.2156815077002414</v>
+        <v>0.2159497542642382</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3878188815590746</v>
+        <v>0.382647963138287</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2164761774495606</v>
+        <v>0.2183761774495606</v>
       </c>
       <c r="C77">
-        <v>-199.937099905799</v>
+        <v>-205.9105827805003</v>
       </c>
       <c r="D77">
-        <v>123.6629000942009</v>
+        <v>122.3014172194997</v>
       </c>
       <c r="E77">
-        <v>90.29999999999998</v>
+        <v>94.91200000000001</v>
       </c>
       <c r="F77">
-        <v>345.9</v>
+        <v>350.512</v>
       </c>
       <c r="G77">
         <v>22.3</v>
@@ -7595,37 +7595,37 @@
         <v>31.21</v>
       </c>
       <c r="M77">
-        <v>81.56322</v>
+        <v>82.65072960000001</v>
       </c>
       <c r="N77">
-        <v>-50.35322000000001</v>
+        <v>-51.44072960000001</v>
       </c>
       <c r="O77">
-        <v>-11.0777084</v>
+        <v>-11.316960512</v>
       </c>
       <c r="P77">
-        <v>-39.2755116</v>
+        <v>-40.12376908800001</v>
       </c>
       <c r="Q77">
-        <v>-38.8855116</v>
+        <v>-39.73376908800001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2180554470055277</v>
+        <v>0.2252327572974246</v>
       </c>
       <c r="T77">
-        <v>2.245065926668858</v>
+        <v>2.33861034028006</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08418255189042315</v>
+        <v>0.08307488673397022</v>
       </c>
       <c r="W77">
-        <v>0.2159497542642382</v>
+        <v>0.2162109417081298</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.382647963138287</v>
+        <v>0.3776131215180464</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2183761774495606</v>
+        <v>0.2202761774495606</v>
       </c>
       <c r="C78">
-        <v>-205.9105827805003</v>
+        <v>-211.8544132694175</v>
       </c>
       <c r="D78">
-        <v>122.3014172194997</v>
+        <v>120.9695867305825</v>
       </c>
       <c r="E78">
-        <v>94.91200000000001</v>
+        <v>99.52400000000003</v>
       </c>
       <c r="F78">
-        <v>350.512</v>
+        <v>355.124</v>
       </c>
       <c r="G78">
         <v>22.3</v>
@@ -7677,37 +7677,37 @@
         <v>31.21</v>
       </c>
       <c r="M78">
-        <v>82.65072960000001</v>
+        <v>83.73823920000001</v>
       </c>
       <c r="N78">
-        <v>-51.44072960000001</v>
+        <v>-52.52823920000002</v>
       </c>
       <c r="O78">
-        <v>-11.316960512</v>
+        <v>-11.556212624</v>
       </c>
       <c r="P78">
-        <v>-40.12376908800001</v>
+        <v>-40.97202657600001</v>
       </c>
       <c r="Q78">
-        <v>-39.73376908800001</v>
+        <v>-40.58202657600001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2252327572974246</v>
+        <v>0.2330341815277475</v>
       </c>
       <c r="T78">
-        <v>2.33861034028006</v>
+        <v>2.440289050727019</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08307488673397022</v>
+        <v>0.0819959921010615</v>
       </c>
       <c r="W78">
-        <v>0.2162109417081298</v>
+        <v>0.2164653450625697</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3776131215180464</v>
+        <v>0.372709055004825</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2202761774495606</v>
+        <v>0.2221761774495606</v>
       </c>
       <c r="C79">
-        <v>-211.8544132694175</v>
+        <v>-217.7695496572885</v>
       </c>
       <c r="D79">
-        <v>120.9695867305825</v>
+        <v>119.6664503427115</v>
       </c>
       <c r="E79">
-        <v>99.52400000000003</v>
+        <v>104.136</v>
       </c>
       <c r="F79">
-        <v>355.124</v>
+        <v>359.736</v>
       </c>
       <c r="G79">
         <v>22.3</v>
@@ -7759,37 +7759,37 @@
         <v>31.21</v>
       </c>
       <c r="M79">
-        <v>83.73823920000001</v>
+        <v>84.8257488</v>
       </c>
       <c r="N79">
-        <v>-52.52823920000002</v>
+        <v>-53.61574880000001</v>
       </c>
       <c r="O79">
-        <v>-11.556212624</v>
+        <v>-11.795464736</v>
       </c>
       <c r="P79">
-        <v>-40.97202657600001</v>
+        <v>-41.82028406400001</v>
       </c>
       <c r="Q79">
-        <v>-40.58202657600001</v>
+        <v>-41.43028406400001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2330341815277475</v>
+        <v>0.2415448261426451</v>
       </c>
       <c r="T79">
-        <v>2.440289050727019</v>
+        <v>2.55121128030552</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0819959921010615</v>
+        <v>0.08094476143309919</v>
       </c>
       <c r="W79">
-        <v>0.2164653450625697</v>
+        <v>0.2167132252540752</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.372709055004825</v>
+        <v>0.3679307337868144</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2221761774495606</v>
+        <v>0.2240761774495606</v>
       </c>
       <c r="C80">
-        <v>-217.7695496572885</v>
+        <v>-223.6569093767074</v>
       </c>
       <c r="D80">
-        <v>119.6664503427115</v>
+        <v>118.3910906232926</v>
       </c>
       <c r="E80">
-        <v>104.136</v>
+        <v>108.748</v>
       </c>
       <c r="F80">
-        <v>359.736</v>
+        <v>364.348</v>
       </c>
       <c r="G80">
         <v>22.3</v>
@@ -7841,37 +7841,37 @@
         <v>31.21</v>
       </c>
       <c r="M80">
-        <v>84.8257488</v>
+        <v>85.9132584</v>
       </c>
       <c r="N80">
-        <v>-53.61574880000001</v>
+        <v>-54.70325840000001</v>
       </c>
       <c r="O80">
-        <v>-11.795464736</v>
+        <v>-12.034716848</v>
       </c>
       <c r="P80">
-        <v>-41.82028406400001</v>
+        <v>-42.66854155200001</v>
       </c>
       <c r="Q80">
-        <v>-41.43028406400001</v>
+        <v>-42.27854155200001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2415448261426451</v>
+        <v>0.2508660083399139</v>
       </c>
       <c r="T80">
-        <v>2.55121128030552</v>
+        <v>2.672697531748641</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08094476143309919</v>
+        <v>0.07992014419976881</v>
       </c>
       <c r="W80">
-        <v>0.2167132252540752</v>
+        <v>0.2169548299976945</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3679307337868144</v>
+        <v>0.3632733827262218</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2240761774495606</v>
+        <v>0.2259761774495606</v>
       </c>
       <c r="C81">
-        <v>-223.6569093767074</v>
+        <v>-229.517371162102</v>
       </c>
       <c r="D81">
-        <v>118.3910906232926</v>
+        <v>117.142628837898</v>
       </c>
       <c r="E81">
-        <v>108.748</v>
+        <v>113.36</v>
       </c>
       <c r="F81">
-        <v>364.348</v>
+        <v>368.96</v>
       </c>
       <c r="G81">
         <v>22.3</v>
@@ -7923,37 +7923,37 @@
         <v>31.21</v>
       </c>
       <c r="M81">
-        <v>85.9132584</v>
+        <v>87.00076800000001</v>
       </c>
       <c r="N81">
-        <v>-54.70325840000001</v>
+        <v>-55.79076800000001</v>
       </c>
       <c r="O81">
-        <v>-12.034716848</v>
+        <v>-12.27396896</v>
       </c>
       <c r="P81">
-        <v>-42.66854155200001</v>
+        <v>-43.51679904000001</v>
       </c>
       <c r="Q81">
-        <v>-42.27854155200001</v>
+        <v>-43.12679904000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2508660083399139</v>
+        <v>0.2611193087569096</v>
       </c>
       <c r="T81">
-        <v>2.672697531748641</v>
+        <v>2.806332408336073</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07992014419976881</v>
+        <v>0.0789211423972717</v>
       </c>
       <c r="W81">
-        <v>0.2169548299976945</v>
+        <v>0.2171903946227234</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3632733827262218</v>
+        <v>0.358732465442144</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2259761774495606</v>
+        <v>0.2278761774495606</v>
       </c>
       <c r="C82">
-        <v>-229.517371162102</v>
+        <v>-235.3517770688476</v>
       </c>
       <c r="D82">
-        <v>117.142628837898</v>
+        <v>115.9202229311525</v>
       </c>
       <c r="E82">
-        <v>113.36</v>
+        <v>117.972</v>
       </c>
       <c r="F82">
-        <v>368.96</v>
+        <v>373.572</v>
       </c>
       <c r="G82">
         <v>22.3</v>
@@ -8005,37 +8005,37 @@
         <v>31.21</v>
       </c>
       <c r="M82">
-        <v>87.00076800000001</v>
+        <v>88.0882776</v>
       </c>
       <c r="N82">
-        <v>-55.79076800000001</v>
+        <v>-56.8782776</v>
       </c>
       <c r="O82">
-        <v>-12.27396896</v>
+        <v>-12.513221072</v>
       </c>
       <c r="P82">
-        <v>-43.51679904000001</v>
+        <v>-44.365056528</v>
       </c>
       <c r="Q82">
-        <v>-43.12679904000001</v>
+        <v>-43.975056528</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2611193087569096</v>
+        <v>0.2724519039546416</v>
       </c>
       <c r="T82">
-        <v>2.806332408336073</v>
+        <v>2.954034114037971</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0789211423972717</v>
+        <v>0.07794680730594737</v>
       </c>
       <c r="W82">
-        <v>0.2171903946227234</v>
+        <v>0.2174201428372576</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.358732465442144</v>
+        <v>0.3543036695724879</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2278761774495606</v>
+        <v>0.2297761774495606</v>
       </c>
       <c r="C83">
-        <v>-235.3517770688476</v>
+        <v>-241.1609343672679</v>
       </c>
       <c r="D83">
-        <v>115.9202229311525</v>
+        <v>114.7230656327322</v>
       </c>
       <c r="E83">
-        <v>117.972</v>
+        <v>122.584</v>
       </c>
       <c r="F83">
-        <v>373.572</v>
+        <v>378.184</v>
       </c>
       <c r="G83">
         <v>22.3</v>
@@ -8087,37 +8087,37 @@
         <v>31.21</v>
       </c>
       <c r="M83">
-        <v>88.0882776</v>
+        <v>89.17578720000002</v>
       </c>
       <c r="N83">
-        <v>-56.8782776</v>
+        <v>-57.96578720000002</v>
       </c>
       <c r="O83">
-        <v>-12.513221072</v>
+        <v>-12.752473184</v>
       </c>
       <c r="P83">
-        <v>-44.365056528</v>
+        <v>-45.21331401600002</v>
       </c>
       <c r="Q83">
-        <v>-43.975056528</v>
+        <v>-44.82331401600002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2724519039546416</v>
+        <v>0.2850436763965662</v>
       </c>
       <c r="T83">
-        <v>2.954034114037971</v>
+        <v>3.118147120373415</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07794680730594737</v>
+        <v>0.07699623648514312</v>
       </c>
       <c r="W83">
-        <v>0.2174201428372576</v>
+        <v>0.2176442874368033</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3543036695724879</v>
+        <v>0.3499828931142869</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2297761774495606</v>
+        <v>0.2316761774495606</v>
       </c>
       <c r="C84">
-        <v>-241.1609343672679</v>
+        <v>-246.9456173204739</v>
       </c>
       <c r="D84">
-        <v>114.7230656327322</v>
+        <v>113.5503826795262</v>
       </c>
       <c r="E84">
-        <v>122.584</v>
+        <v>127.1960000000001</v>
       </c>
       <c r="F84">
-        <v>378.184</v>
+        <v>382.796</v>
       </c>
       <c r="G84">
         <v>22.3</v>
@@ -8169,37 +8169,37 @@
         <v>31.21</v>
       </c>
       <c r="M84">
-        <v>89.17578720000002</v>
+        <v>90.26329680000002</v>
       </c>
       <c r="N84">
-        <v>-57.96578720000002</v>
+        <v>-59.05329680000003</v>
       </c>
       <c r="O84">
-        <v>-12.752473184</v>
+        <v>-12.99172529600001</v>
       </c>
       <c r="P84">
-        <v>-45.21331401600002</v>
+        <v>-46.06157150400002</v>
       </c>
       <c r="Q84">
-        <v>-44.82331401600002</v>
+        <v>-45.67157150400002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2850436763965662</v>
+        <v>0.2991168338316584</v>
       </c>
       <c r="T84">
-        <v>3.118147120373415</v>
+        <v>3.301567539218909</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07699623648514312</v>
+        <v>0.07606857098532212</v>
       </c>
       <c r="W84">
-        <v>0.2176442874368033</v>
+        <v>0.217863030961661</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3499828931142869</v>
+        <v>0.345766231751464</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2316761774495606</v>
+        <v>0.2335761774495606</v>
       </c>
       <c r="C85">
-        <v>-246.9456173204739</v>
+        <v>-252.7065688542702</v>
       </c>
       <c r="D85">
-        <v>113.5503826795262</v>
+        <v>112.4014311457298</v>
       </c>
       <c r="E85">
-        <v>127.1960000000001</v>
+        <v>131.808</v>
       </c>
       <c r="F85">
-        <v>382.796</v>
+        <v>387.408</v>
       </c>
       <c r="G85">
         <v>22.3</v>
@@ -8251,37 +8251,37 @@
         <v>31.21</v>
       </c>
       <c r="M85">
-        <v>90.26329680000002</v>
+        <v>91.35080640000001</v>
       </c>
       <c r="N85">
-        <v>-59.05329680000003</v>
+        <v>-60.14080640000002</v>
       </c>
       <c r="O85">
-        <v>-12.99172529600001</v>
+        <v>-13.230977408</v>
       </c>
       <c r="P85">
-        <v>-46.06157150400002</v>
+        <v>-46.90982899200002</v>
       </c>
       <c r="Q85">
-        <v>-45.67157150400002</v>
+        <v>-46.51982899200001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2991168338316584</v>
+        <v>0.3149491359461371</v>
       </c>
       <c r="T85">
-        <v>3.301567539218909</v>
+        <v>3.507915510420092</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07606857098532212</v>
+        <v>0.07516299275930638</v>
       </c>
       <c r="W85">
-        <v>0.217863030961661</v>
+        <v>0.2180765663073556</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.345766231751464</v>
+        <v>0.3416499670877562</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2335761774495606</v>
+        <v>0.2354761774495606</v>
       </c>
       <c r="C86">
-        <v>-252.7065688542702</v>
+        <v>-258.4445021266954</v>
       </c>
       <c r="D86">
-        <v>112.4014311457298</v>
+        <v>111.2754978733046</v>
       </c>
       <c r="E86">
-        <v>131.808</v>
+        <v>136.42</v>
       </c>
       <c r="F86">
-        <v>387.408</v>
+        <v>392.02</v>
       </c>
       <c r="G86">
         <v>22.3</v>
@@ -8333,37 +8333,37 @@
         <v>31.21</v>
       </c>
       <c r="M86">
-        <v>91.3508064</v>
+        <v>92.438316</v>
       </c>
       <c r="N86">
-        <v>-60.1408064</v>
+        <v>-61.22831600000001</v>
       </c>
       <c r="O86">
-        <v>-13.230977408</v>
+        <v>-13.47022952</v>
       </c>
       <c r="P86">
-        <v>-46.909828992</v>
+        <v>-47.75808648</v>
       </c>
       <c r="Q86">
-        <v>-46.519828992</v>
+        <v>-47.36808648</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3149491359461369</v>
+        <v>0.3328924116758794</v>
       </c>
       <c r="T86">
-        <v>3.50791551042009</v>
+        <v>3.741776544448096</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07516299275930639</v>
+        <v>0.07427872225625573</v>
       </c>
       <c r="W86">
-        <v>0.2180765663073556</v>
+        <v>0.2182850772919749</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3416499670877563</v>
+        <v>0.3376305557102532</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2354761774495606</v>
+        <v>0.2373761774495606</v>
       </c>
       <c r="C87">
-        <v>-258.4445021266954</v>
+        <v>-264.1601020041642</v>
       </c>
       <c r="D87">
-        <v>111.2754978733046</v>
+        <v>110.1718979958358</v>
       </c>
       <c r="E87">
-        <v>136.42</v>
+        <v>141.032</v>
       </c>
       <c r="F87">
-        <v>392.02</v>
+        <v>396.632</v>
       </c>
       <c r="G87">
         <v>22.3</v>
@@ -8415,37 +8415,37 @@
         <v>31.21</v>
       </c>
       <c r="M87">
-        <v>92.438316</v>
+        <v>93.5258256</v>
       </c>
       <c r="N87">
-        <v>-61.22831600000001</v>
+        <v>-62.31582560000001</v>
       </c>
       <c r="O87">
-        <v>-13.47022952</v>
+        <v>-13.709481632</v>
       </c>
       <c r="P87">
-        <v>-47.75808648</v>
+        <v>-48.606343968</v>
       </c>
       <c r="Q87">
-        <v>-47.36808648</v>
+        <v>-48.216343968</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3328924116758794</v>
+        <v>0.3533990125098708</v>
       </c>
       <c r="T87">
-        <v>3.741776544448096</v>
+        <v>4.009046297622961</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07427872225625573</v>
+        <v>0.07341501618350856</v>
       </c>
       <c r="W87">
-        <v>0.2182850772919749</v>
+        <v>0.2184887391839287</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3376305557102532</v>
+        <v>0.3337046190159479</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2373761774495606</v>
+        <v>0.2392761774495606</v>
       </c>
       <c r="C88">
-        <v>-264.1601020041642</v>
+        <v>-269.8540264506334</v>
       </c>
       <c r="D88">
-        <v>110.1718979958358</v>
+        <v>109.0899735493666</v>
       </c>
       <c r="E88">
-        <v>141.032</v>
+        <v>145.644</v>
       </c>
       <c r="F88">
-        <v>396.632</v>
+        <v>401.244</v>
       </c>
       <c r="G88">
         <v>22.3</v>
@@ -8497,37 +8497,37 @@
         <v>31.21</v>
       </c>
       <c r="M88">
-        <v>93.5258256</v>
+        <v>94.61333519999999</v>
       </c>
       <c r="N88">
-        <v>-62.31582560000001</v>
+        <v>-63.4033352</v>
       </c>
       <c r="O88">
-        <v>-13.709481632</v>
+        <v>-13.948733744</v>
       </c>
       <c r="P88">
-        <v>-48.606343968</v>
+        <v>-49.454601456</v>
       </c>
       <c r="Q88">
-        <v>-48.216343968</v>
+        <v>-49.064601456</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3533990125098708</v>
+        <v>0.3770604750106301</v>
       </c>
       <c r="T88">
-        <v>4.009046297622961</v>
+        <v>4.317434474363188</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07341501618350856</v>
+        <v>0.07257116542277858</v>
       </c>
       <c r="W88">
-        <v>0.2184887391839287</v>
+        <v>0.2186877191933088</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3337046190159479</v>
+        <v>0.3298689337399026</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2392761774495606</v>
+        <v>0.2411761774495606</v>
       </c>
       <c r="C89">
-        <v>-269.8540264506334</v>
+        <v>-275.5269078357107</v>
       </c>
       <c r="D89">
-        <v>109.0899735493666</v>
+        <v>108.0290921642893</v>
       </c>
       <c r="E89">
-        <v>145.644</v>
+        <v>150.256</v>
       </c>
       <c r="F89">
-        <v>401.244</v>
+        <v>405.856</v>
       </c>
       <c r="G89">
         <v>22.3</v>
@@ -8579,37 +8579,37 @@
         <v>31.21</v>
       </c>
       <c r="M89">
-        <v>94.61333519999999</v>
+        <v>95.7008448</v>
       </c>
       <c r="N89">
-        <v>-63.4033352</v>
+        <v>-64.4908448</v>
       </c>
       <c r="O89">
-        <v>-13.948733744</v>
+        <v>-14.187985856</v>
       </c>
       <c r="P89">
-        <v>-49.454601456</v>
+        <v>-50.30285894400001</v>
       </c>
       <c r="Q89">
-        <v>-49.064601456</v>
+        <v>-49.91285894400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3770604750106301</v>
+        <v>0.4046655145948493</v>
       </c>
       <c r="T89">
-        <v>4.317434474363188</v>
+        <v>4.67722068056012</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07257116542277858</v>
+        <v>0.07174649308842881</v>
       </c>
       <c r="W89">
-        <v>0.2186877191933088</v>
+        <v>0.2188821769297485</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3298689337399026</v>
+        <v>0.3261204231292218</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2411761774495606</v>
+        <v>0.2430761774495606</v>
       </c>
       <c r="C90">
-        <v>-275.5269078357107</v>
+        <v>-281.1793541671722</v>
       </c>
       <c r="D90">
-        <v>108.0290921642893</v>
+        <v>106.9886458328278</v>
       </c>
       <c r="E90">
-        <v>150.256</v>
+        <v>154.868</v>
       </c>
       <c r="F90">
-        <v>405.856</v>
+        <v>410.468</v>
       </c>
       <c r="G90">
         <v>22.3</v>
@@ -8661,37 +8661,37 @@
         <v>31.21</v>
       </c>
       <c r="M90">
-        <v>95.7008448</v>
+        <v>96.7883544</v>
       </c>
       <c r="N90">
-        <v>-64.4908448</v>
+        <v>-65.57835440000001</v>
       </c>
       <c r="O90">
-        <v>-14.187985856</v>
+        <v>-14.427237968</v>
       </c>
       <c r="P90">
-        <v>-50.30285894400001</v>
+        <v>-51.15111643200001</v>
       </c>
       <c r="Q90">
-        <v>-49.91285894400001</v>
+        <v>-50.76111643200001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4046655145948493</v>
+        <v>0.4372896522852902</v>
       </c>
       <c r="T90">
-        <v>4.67722068056012</v>
+        <v>5.102422560611041</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07174649308842881</v>
+        <v>0.07094035271664872</v>
       </c>
       <c r="W90">
-        <v>0.2188821769297485</v>
+        <v>0.2190722648294142</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3261204231292218</v>
+        <v>0.3224561487120396</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2430761774495606</v>
+        <v>0.2449761774495606</v>
       </c>
       <c r="C91">
-        <v>-281.1793541671722</v>
+        <v>-286.8119502529357</v>
       </c>
       <c r="D91">
-        <v>106.9886458328278</v>
+        <v>105.9680497470642</v>
       </c>
       <c r="E91">
-        <v>154.868</v>
+        <v>159.48</v>
       </c>
       <c r="F91">
-        <v>410.468</v>
+        <v>415.08</v>
       </c>
       <c r="G91">
         <v>22.3</v>
@@ -8743,37 +8743,37 @@
         <v>31.21</v>
       </c>
       <c r="M91">
-        <v>96.7883544</v>
+        <v>97.87586400000001</v>
       </c>
       <c r="N91">
-        <v>-65.57835440000001</v>
+        <v>-66.66586400000001</v>
       </c>
       <c r="O91">
-        <v>-14.427237968</v>
+        <v>-14.66649008</v>
       </c>
       <c r="P91">
-        <v>-51.15111643200001</v>
+        <v>-51.99937392000001</v>
       </c>
       <c r="Q91">
-        <v>-50.76111643200001</v>
+        <v>-51.60937392000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4372896522852902</v>
+        <v>0.4764386175138192</v>
       </c>
       <c r="T91">
-        <v>5.102422560611041</v>
+        <v>5.612664816672146</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07094035271664872</v>
+        <v>0.07015212657535262</v>
       </c>
       <c r="W91">
-        <v>0.2190722648294142</v>
+        <v>0.2192581285535319</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3224561487120396</v>
+        <v>0.3188733026152392</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2449761774495606</v>
+        <v>0.2468761774495606</v>
       </c>
       <c r="C92">
-        <v>-286.8119502529357</v>
+        <v>-292.4252587971562</v>
       </c>
       <c r="D92">
-        <v>105.9680497470642</v>
+        <v>104.9667412028438</v>
       </c>
       <c r="E92">
-        <v>159.48</v>
+        <v>164.092</v>
       </c>
       <c r="F92">
-        <v>415.08</v>
+        <v>419.692</v>
       </c>
       <c r="G92">
         <v>22.3</v>
@@ -8825,37 +8825,37 @@
         <v>31.21</v>
       </c>
       <c r="M92">
-        <v>97.87586400000001</v>
+        <v>98.96337360000001</v>
       </c>
       <c r="N92">
-        <v>-66.66586400000001</v>
+        <v>-67.75337360000002</v>
       </c>
       <c r="O92">
-        <v>-14.66649008</v>
+        <v>-14.905742192</v>
       </c>
       <c r="P92">
-        <v>-51.99937392000001</v>
+        <v>-52.84763140800001</v>
       </c>
       <c r="Q92">
-        <v>-51.60937392000001</v>
+        <v>-52.45763140800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4764386175138192</v>
+        <v>0.5242873527931324</v>
       </c>
       <c r="T92">
-        <v>5.612664816672146</v>
+        <v>6.236294240746829</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07015212657535262</v>
+        <v>0.06938122408551357</v>
       </c>
       <c r="W92">
-        <v>0.2192581285535319</v>
+        <v>0.2194399073606359</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3188733026152392</v>
+        <v>0.3153692003886981</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2468761774495606</v>
+        <v>0.2487761774495606</v>
       </c>
       <c r="C93">
-        <v>-292.4252587971562</v>
+        <v>-298.0198214347591</v>
       </c>
       <c r="D93">
-        <v>104.9667412028438</v>
+        <v>103.9841785652409</v>
       </c>
       <c r="E93">
-        <v>164.092</v>
+        <v>168.704</v>
       </c>
       <c r="F93">
-        <v>419.692</v>
+        <v>424.304</v>
       </c>
       <c r="G93">
         <v>22.3</v>
@@ -8907,37 +8907,37 @@
         <v>31.21</v>
       </c>
       <c r="M93">
-        <v>98.96337360000001</v>
+        <v>100.0508832</v>
       </c>
       <c r="N93">
-        <v>-67.75337360000002</v>
+        <v>-68.84088320000002</v>
       </c>
       <c r="O93">
-        <v>-14.905742192</v>
+        <v>-15.144994304</v>
       </c>
       <c r="P93">
-        <v>-52.84763140800001</v>
+        <v>-53.69588889600001</v>
       </c>
       <c r="Q93">
-        <v>-52.45763140800001</v>
+        <v>-53.30588889600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5242873527931324</v>
+        <v>0.5840982718922743</v>
       </c>
       <c r="T93">
-        <v>6.236294240746829</v>
+        <v>7.015831020840185</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06938122408551357</v>
+        <v>0.06862708034545364</v>
       </c>
       <c r="W93">
-        <v>0.2194399073606359</v>
+        <v>0.2196177344545421</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3153692003886981</v>
+        <v>0.3119412742975165</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2487761774495606</v>
+        <v>0.2506761774495606</v>
       </c>
       <c r="C94">
-        <v>-298.0198214347591</v>
+        <v>-303.5961597084103</v>
       </c>
       <c r="D94">
-        <v>103.9841785652409</v>
+        <v>103.0198402915897</v>
       </c>
       <c r="E94">
-        <v>168.704</v>
+        <v>173.316</v>
       </c>
       <c r="F94">
-        <v>424.304</v>
+        <v>428.916</v>
       </c>
       <c r="G94">
         <v>22.3</v>
@@ -8989,37 +8989,37 @@
         <v>31.21</v>
       </c>
       <c r="M94">
-        <v>100.0508832</v>
+        <v>101.1383928</v>
       </c>
       <c r="N94">
-        <v>-68.84088320000002</v>
+        <v>-69.92839280000001</v>
       </c>
       <c r="O94">
-        <v>-15.144994304</v>
+        <v>-15.384246416</v>
       </c>
       <c r="P94">
-        <v>-53.69588889600001</v>
+        <v>-54.54414638400001</v>
       </c>
       <c r="Q94">
-        <v>-53.30588889600001</v>
+        <v>-54.15414638400001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5840982718922743</v>
+        <v>0.660998025019742</v>
       </c>
       <c r="T94">
-        <v>7.015831020840185</v>
+        <v>8.018092595245927</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06862708034545364</v>
+        <v>0.06788915475034125</v>
       </c>
       <c r="W94">
-        <v>0.2196177344545421</v>
+        <v>0.2197917373098695</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3119412742975165</v>
+        <v>0.3085870670470057</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2506761774495606</v>
+        <v>0.2525761774495606</v>
       </c>
       <c r="C95">
-        <v>-303.5961597084103</v>
+        <v>-309.154775991622</v>
       </c>
       <c r="D95">
-        <v>103.0198402915897</v>
+        <v>102.073224008378</v>
       </c>
       <c r="E95">
-        <v>173.316</v>
+        <v>177.928</v>
       </c>
       <c r="F95">
-        <v>428.916</v>
+        <v>433.528</v>
       </c>
       <c r="G95">
         <v>22.3</v>
@@ -9071,37 +9071,37 @@
         <v>31.21</v>
       </c>
       <c r="M95">
-        <v>101.1383928</v>
+        <v>102.2259024</v>
       </c>
       <c r="N95">
-        <v>-69.92839280000001</v>
+        <v>-71.01590240000002</v>
       </c>
       <c r="O95">
-        <v>-15.384246416</v>
+        <v>-15.623498528</v>
       </c>
       <c r="P95">
-        <v>-54.54414638400001</v>
+        <v>-55.39240387200001</v>
       </c>
       <c r="Q95">
-        <v>-54.15414638400001</v>
+        <v>-55.00240387200001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.660998025019742</v>
+        <v>0.7635310291896992</v>
       </c>
       <c r="T95">
-        <v>8.018092595245927</v>
+        <v>9.35444136112025</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06788915475034125</v>
+        <v>0.0671669296998057</v>
       </c>
       <c r="W95">
-        <v>0.2197917373098695</v>
+        <v>0.2199620379767858</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3085870670470057</v>
+        <v>0.3053042259082077</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2525761774495606</v>
+        <v>0.2544761774495606</v>
       </c>
       <c r="C96">
-        <v>-309.154775991622</v>
+        <v>-314.6961543614304</v>
       </c>
       <c r="D96">
-        <v>102.073224008378</v>
+        <v>101.1438456385697</v>
       </c>
       <c r="E96">
-        <v>177.928</v>
+        <v>182.54</v>
       </c>
       <c r="F96">
-        <v>433.528</v>
+        <v>438.14</v>
       </c>
       <c r="G96">
         <v>22.3</v>
@@ -9153,37 +9153,37 @@
         <v>31.21</v>
       </c>
       <c r="M96">
-        <v>102.2259024</v>
+        <v>103.313412</v>
       </c>
       <c r="N96">
-        <v>-71.01590240000002</v>
+        <v>-72.10341200000002</v>
       </c>
       <c r="O96">
-        <v>-15.623498528</v>
+        <v>-15.86275064000001</v>
       </c>
       <c r="P96">
-        <v>-55.39240387200001</v>
+        <v>-56.24066136000002</v>
       </c>
       <c r="Q96">
-        <v>-55.00240387200001</v>
+        <v>-55.85066136000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7635310291896992</v>
+        <v>0.9070772350276395</v>
       </c>
       <c r="T96">
-        <v>9.35444136112025</v>
+        <v>11.22532963334431</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0671669296998057</v>
+        <v>0.06645990938717616</v>
       </c>
       <c r="W96">
-        <v>0.2199620379767858</v>
+        <v>0.2201287533665039</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3053042259082077</v>
+        <v>0.302090497214437</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2544761774495606</v>
+        <v>0.2563761774495606</v>
       </c>
       <c r="C97">
-        <v>-314.6961543614304</v>
+        <v>-320.2207614238285</v>
       </c>
       <c r="D97">
-        <v>101.1438456385697</v>
+        <v>100.2312385761715</v>
       </c>
       <c r="E97">
-        <v>182.54</v>
+        <v>187.152</v>
       </c>
       <c r="F97">
-        <v>438.14</v>
+        <v>442.752</v>
       </c>
       <c r="G97">
         <v>22.3</v>
@@ -9235,37 +9235,37 @@
         <v>31.21</v>
       </c>
       <c r="M97">
-        <v>103.313412</v>
+        <v>104.4009216</v>
       </c>
       <c r="N97">
-        <v>-72.10341200000002</v>
+        <v>-73.19092160000001</v>
       </c>
       <c r="O97">
-        <v>-15.86275064000001</v>
+        <v>-16.102002752</v>
       </c>
       <c r="P97">
-        <v>-56.24066136000002</v>
+        <v>-57.08891884800001</v>
       </c>
       <c r="Q97">
-        <v>-55.85066136000002</v>
+        <v>-56.69891884800001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9070772350276395</v>
+        <v>1.12239654378455</v>
       </c>
       <c r="T97">
-        <v>11.22532963334431</v>
+        <v>14.03166204168039</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06645990938717616</v>
+        <v>0.06576761866439308</v>
       </c>
       <c r="W97">
-        <v>0.2201287533665039</v>
+        <v>0.2202919955189361</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.302090497214437</v>
+        <v>0.2989437212017867</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2563761774495606</v>
+        <v>0.2582761774495606</v>
       </c>
       <c r="C98">
-        <v>-320.2207614238285</v>
+        <v>-325.7290470949124</v>
       </c>
       <c r="D98">
-        <v>100.2312385761715</v>
+        <v>99.33495290508756</v>
       </c>
       <c r="E98">
-        <v>187.152</v>
+        <v>191.764</v>
       </c>
       <c r="F98">
-        <v>442.752</v>
+        <v>447.364</v>
       </c>
       <c r="G98">
         <v>22.3</v>
@@ -9317,37 +9317,37 @@
         <v>31.21</v>
       </c>
       <c r="M98">
-        <v>104.4009216</v>
+        <v>105.4884312</v>
       </c>
       <c r="N98">
-        <v>-73.1909216</v>
+        <v>-74.2784312</v>
       </c>
       <c r="O98">
-        <v>-16.102002752</v>
+        <v>-16.341254864</v>
       </c>
       <c r="P98">
-        <v>-57.08891884799999</v>
+        <v>-57.937176336</v>
       </c>
       <c r="Q98">
-        <v>-56.69891884799999</v>
+        <v>-57.547176336</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.122396543784547</v>
+        <v>1.481262058379396</v>
       </c>
       <c r="T98">
-        <v>14.03166204168035</v>
+        <v>18.70888272224047</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0657676186643931</v>
+        <v>0.0650896019771313</v>
       </c>
       <c r="W98">
-        <v>0.2202919955189361</v>
+        <v>0.2204518718537924</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2989437212017868</v>
+        <v>0.2958618271687786</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2582761774495606</v>
+        <v>0.2601761774495606</v>
       </c>
       <c r="C99">
-        <v>-325.7290470949124</v>
+        <v>-331.2214453404874</v>
       </c>
       <c r="D99">
-        <v>99.33495290508756</v>
+        <v>98.45455465951257</v>
       </c>
       <c r="E99">
-        <v>191.764</v>
+        <v>196.376</v>
       </c>
       <c r="F99">
-        <v>447.364</v>
+        <v>451.976</v>
       </c>
       <c r="G99">
         <v>22.3</v>
@@ -9399,37 +9399,37 @@
         <v>31.21</v>
       </c>
       <c r="M99">
-        <v>105.4884312</v>
+        <v>106.5759408</v>
       </c>
       <c r="N99">
-        <v>-74.2784312</v>
+        <v>-75.3659408</v>
       </c>
       <c r="O99">
-        <v>-16.341254864</v>
+        <v>-16.580506976</v>
       </c>
       <c r="P99">
-        <v>-57.937176336</v>
+        <v>-58.785433824</v>
       </c>
       <c r="Q99">
-        <v>-57.547176336</v>
+        <v>-58.395433824</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.481262058379396</v>
+        <v>2.198993087569094</v>
       </c>
       <c r="T99">
-        <v>18.70888272224047</v>
+        <v>28.0633240833607</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0650896019771313</v>
+        <v>0.06442542236511975</v>
       </c>
       <c r="W99">
-        <v>0.2204518718537924</v>
+        <v>0.2206084854063048</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2958618271687786</v>
+        <v>0.2928428289323625</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2601761774495606</v>
+        <v>0.2620761774495606</v>
       </c>
       <c r="C100">
-        <v>-331.2214453404874</v>
+        <v>-336.6983748766897</v>
       </c>
       <c r="D100">
-        <v>98.45455465951257</v>
+        <v>97.5896251233102</v>
       </c>
       <c r="E100">
-        <v>196.376</v>
+        <v>200.988</v>
       </c>
       <c r="F100">
-        <v>451.976</v>
+        <v>456.588</v>
       </c>
       <c r="G100">
         <v>22.3</v>
@@ -9481,37 +9481,37 @@
         <v>31.21</v>
       </c>
       <c r="M100">
-        <v>106.5759408</v>
+        <v>107.6634504</v>
       </c>
       <c r="N100">
-        <v>-75.3659408</v>
+        <v>-76.45345040000001</v>
       </c>
       <c r="O100">
-        <v>-16.580506976</v>
+        <v>-16.819759088</v>
       </c>
       <c r="P100">
-        <v>-58.785433824</v>
+        <v>-59.63369131200001</v>
       </c>
       <c r="Q100">
-        <v>-58.395433824</v>
+        <v>-59.24369131200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.198993087569094</v>
+        <v>4.352186175138187</v>
       </c>
       <c r="T100">
-        <v>28.0633240833607</v>
+        <v>56.1266481667214</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06442542236511975</v>
+        <v>0.06377466052304784</v>
       </c>
       <c r="W100">
-        <v>0.2206084854063048</v>
+        <v>0.2207619350486653</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2928428289323625</v>
+        <v>0.2898848205593083</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2620761774495606</v>
-      </c>
-      <c r="C101">
-        <v>-336.6983748766897</v>
-      </c>
-      <c r="D101">
-        <v>97.5896251233102</v>
-      </c>
-      <c r="E101">
-        <v>200.988</v>
-      </c>
-      <c r="F101">
-        <v>456.588</v>
-      </c>
-      <c r="G101">
-        <v>22.3</v>
-      </c>
-      <c r="H101">
-        <v>205.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.6</v>
-      </c>
-      <c r="K101">
-        <v>0.39</v>
-      </c>
-      <c r="L101">
-        <v>31.21</v>
-      </c>
-      <c r="M101">
-        <v>107.6634504</v>
-      </c>
-      <c r="N101">
-        <v>-76.45345040000001</v>
-      </c>
-      <c r="O101">
-        <v>-16.819759088</v>
-      </c>
-      <c r="P101">
-        <v>-59.63369131200001</v>
-      </c>
-      <c r="Q101">
-        <v>-59.24369131200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.352186175138187</v>
-      </c>
-      <c r="T101">
-        <v>56.1266481667214</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06377466052304784</v>
-      </c>
-      <c r="W101">
-        <v>0.2207619350486653</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2898848205593083</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
